--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -54,7 +54,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -261,7 +261,7 @@
     <t>Total PUBLIC FUNDING</t>
   </si>
   <si>
-    <t>GRANTS, CONTRIBUTIONS &amp; OTHER SUPPORT</t>
+    <t>PHILANTHROPY</t>
   </si>
   <si>
     <t>CSP Startup Grant</t>
@@ -270,7 +270,7 @@
     <t>Annual Fundraising</t>
   </si>
   <si>
-    <t>Total GRANTS, CONTRIBUTIONS &amp; OTHER SUPPORT</t>
+    <t>Total PHILANTHROPY</t>
   </si>
   <si>
     <t>OTHER REVENUE</t>
@@ -547,7 +547,7 @@
     </font>
     <font>
       <color rgb="FF94A3B8"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -591,7 +591,7 @@
     <font>
       <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -615,7 +615,7 @@
     <font>
       <i/>
       <color rgb="FF888888"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1567,25 +1567,25 @@
       <c r="A11" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="27" t="str">
         <f>SUM(B9:B10)</f>
-        <v>175000</v>
-      </c>
-      <c r="C11" s="27">
+        <v>0</v>
+      </c>
+      <c r="C11" s="27" t="str">
         <f>SUM(C9:C10)</f>
-        <v>135000</v>
-      </c>
-      <c r="D11" s="27">
+        <v>0</v>
+      </c>
+      <c r="D11" s="27" t="str">
         <f>SUM(D9:D10)</f>
-        <v>95000</v>
-      </c>
-      <c r="E11" s="27">
+        <v>0</v>
+      </c>
+      <c r="E11" s="27" t="str">
         <f>SUM(E9:E10)</f>
-        <v>55000</v>
-      </c>
-      <c r="F11" s="27">
+        <v>0</v>
+      </c>
+      <c r="F11" s="27" t="str">
         <f>SUM(F9:F10)</f>
-        <v>65000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -102,7 +102,7 @@
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Assumptions</t>
+    <t>SchoolStack Budget - Assumptions</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -285,7 +285,7 @@
     <t>TOTAL NET REVENUE</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Staffing &amp; Personnel</t>
+    <t>SchoolStack Budget - Staffing &amp; Personnel</t>
   </si>
   <si>
     <t>Role</t>
@@ -483,7 +483,7 @@
     <t>Enrollment Growth %</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>KEY RATIOS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -54,7 +54,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -54,7 +54,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -525,7 +525,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -601,6 +601,16 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -631,7 +641,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -650,6 +660,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
@@ -664,7 +679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -697,6 +712,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF93C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
@@ -715,7 +739,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -736,11 +760,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -750,16 +775,17 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="17" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1329,7 +1355,7 @@
       <c r="A32" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="24" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1359,22 +1385,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1382,23 +1408,23 @@
       <c r="A2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="26">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="26">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="26">
         <f>Assumptions!B25</f>
         <v>400</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <f>Assumptions!B26</f>
         <v>500</v>
       </c>
@@ -1417,23 +1443,23 @@
       <c r="A4" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>8500*Assumptions!B22</f>
         <v>1020000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>8670*Assumptions!B23</f>
         <v>1734000</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>8843*Assumptions!B24</f>
         <v>2652900</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>9020*Assumptions!B25</f>
         <v>3608000</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>9200*Assumptions!B26</f>
         <v>4600000</v>
       </c>
@@ -1442,23 +1468,23 @@
       <c r="A5" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>750*Assumptions!B22</f>
         <v>90000</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>765*Assumptions!B23</f>
         <v>153000</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>780*Assumptions!B24</f>
         <v>234000</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>796*Assumptions!B25</f>
         <v>318400</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>812*Assumptions!B26</f>
         <v>406000</v>
       </c>
@@ -1467,23 +1493,23 @@
       <c r="A6" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <f>1100*Assumptions!B22</f>
         <v>132000</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>1122*Assumptions!B23</f>
         <v>224400</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>1144*Assumptions!B24</f>
         <v>343200</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>1167*Assumptions!B25</f>
         <v>466800</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>1191*Assumptions!B26</f>
         <v>595500</v>
       </c>
@@ -1492,23 +1518,23 @@
       <c r="A7" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>SUM(B4:B6)</f>
         <v>1242000</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>SUM(C4:C6)</f>
         <v>2111400</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>SUM(D4:D6)</f>
         <v>3230100</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>SUM(E4:E6)</f>
         <v>4393200</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <f>SUM(F4:F6)</f>
         <v>5601500</v>
       </c>
@@ -1527,19 +1553,19 @@
       <c r="A9" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <v>150000</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <v>100000</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <v>50000</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <v>0</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <v>0</v>
       </c>
     </row>
@@ -1547,19 +1573,19 @@
       <c r="A10" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>25000</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <v>35000</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <v>45000</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <v>55000</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <v>65000</v>
       </c>
     </row>
@@ -1567,23 +1593,23 @@
       <c r="A11" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="28" t="str">
         <f>SUM(B9:B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="27" t="str">
+      <c r="C11" s="28" t="str">
         <f>SUM(C9:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="27" t="str">
+      <c r="D11" s="28" t="str">
         <f>SUM(D9:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="27" t="str">
+      <c r="E11" s="28" t="str">
         <f>SUM(E9:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="27" t="str">
+      <c r="F11" s="28" t="str">
         <f>SUM(F9:F10)</f>
         <v>0</v>
       </c>
@@ -1602,23 +1628,23 @@
       <c r="A13" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <f>400*Assumptions!B22</f>
         <v>48000</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <f>412*Assumptions!B23</f>
         <v>82400</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>424*Assumptions!B24</f>
         <v>127200</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>437*Assumptions!B25</f>
         <v>174800</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>450*Assumptions!B26</f>
         <v>225000</v>
       </c>
@@ -1627,23 +1653,23 @@
       <c r="A14" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <f>SUM(B13:B13)</f>
         <v>48000</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>SUM(C13:C13)</f>
         <v>82400</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>SUM(D13:D13)</f>
         <v>127200</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>SUM(E13:E13)</f>
         <v>174800</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f>SUM(F13:F13)</f>
         <v>225000</v>
       </c>
@@ -1652,23 +1678,23 @@
       <c r="A16" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="28">
         <f>B7+B11+B14</f>
         <v>1465000</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>C7+C11+C14</f>
         <v>2328800</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>D7+D11+D14</f>
         <v>3452300</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>E7+E11+E14</f>
         <v>4623000</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <f>F7+F11+F14</f>
         <v>5891500</v>
       </c>
@@ -1708,28 +1734,28 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="25" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1743,19 +1769,19 @@
       <c r="C4" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <v>1</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>105000</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>0.26</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="32">
         <v>140332.5</v>
       </c>
     </row>
@@ -1769,19 +1795,19 @@
       <c r="C5" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <v>1</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>82000</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>0.26</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <v>109593</v>
       </c>
     </row>
@@ -1795,19 +1821,19 @@
       <c r="C6" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <v>5</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>50000</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>0.26</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <v>334125</v>
       </c>
     </row>
@@ -1821,19 +1847,19 @@
       <c r="C7" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <v>1</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>53000</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>0.26</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <v>70834.5</v>
       </c>
     </row>
@@ -1847,19 +1873,19 @@
       <c r="C8" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>3</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>28000</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>0.18</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <v>105546</v>
       </c>
     </row>
@@ -1873,19 +1899,19 @@
       <c r="C9" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>62000</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>0.26</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <v>82863</v>
       </c>
     </row>
@@ -1899,19 +1925,19 @@
       <c r="C10" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <v>2</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>36000</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>0.22</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <v>0.0765</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <v>93348</v>
       </c>
     </row>
@@ -1931,7 +1957,7 @@
       <c r="A13" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="33">
         <v>7</v>
       </c>
     </row>
@@ -1939,7 +1965,7 @@
       <c r="A14" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="33">
         <v>14</v>
       </c>
     </row>
@@ -1947,7 +1973,7 @@
       <c r="A15" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>708000</v>
       </c>
     </row>
@@ -1955,7 +1981,7 @@
       <c r="A16" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <v>174480</v>
       </c>
     </row>
@@ -1963,7 +1989,7 @@
       <c r="A17" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <v>54162</v>
       </c>
     </row>
@@ -1971,15 +1997,15 @@
       <c r="A18" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="32">
         <v>936642</v>
       </c>
     </row>
@@ -1994,22 +2020,22 @@
       <c r="F21" s="8"/>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2017,19 +2043,19 @@
       <c r="A23" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="27">
         <v>936642</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="27">
         <v>936642</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="27">
         <v>936642</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="27">
         <v>936642</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="27">
         <v>936642</v>
       </c>
     </row>
@@ -2037,23 +2063,23 @@
       <c r="A24" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="34">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="34">
         <f>(1+Assumptions!B29)^1</f>
         <v>1</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="34">
         <f>(1+Assumptions!B29)^2</f>
         <v>1</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="34">
         <f>(1+Assumptions!B29)^3</f>
         <v>1</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="34">
         <f>(1+Assumptions!B29)^4</f>
         <v>1</v>
       </c>
@@ -2062,20 +2088,20 @@
       <c r="A25" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="35">
         <f>Assumptions!B31</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="35">
         <v>1</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="35">
         <v>1</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="35">
         <v>1</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="35">
         <v>1</v>
       </c>
     </row>
@@ -2083,23 +2109,23 @@
       <c r="A26" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="28">
         <f>B23*B24*B25</f>
         <v>780535</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="28">
         <f>C23*C24*C25</f>
         <v>936642</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>D23*D24*D25</f>
         <v>936642</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>E23*E24*E25</f>
         <v>936642</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="28">
         <f>F23*F24*F25</f>
         <v>936642</v>
       </c>
@@ -2130,22 +2156,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2153,23 +2179,23 @@
       <c r="A2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="26">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="26">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="26">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="26">
         <f>Assumptions!B25</f>
         <v>400</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <f>Assumptions!B26</f>
         <v>500</v>
       </c>
@@ -2188,23 +2214,23 @@
       <c r="A4" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>650*Assumptions!B22</f>
         <v>78000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>670*Assumptions!B23</f>
         <v>134000</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>690*Assumptions!B24</f>
         <v>207000</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>710*Assumptions!B25</f>
         <v>284000</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>732*Assumptions!B26</f>
         <v>366000</v>
       </c>
@@ -2213,23 +2239,23 @@
       <c r="A5" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>SUM(B4:B4)</f>
         <v>78000</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <f>SUM(C4:C4)</f>
         <v>134000</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>SUM(D4:D4)</f>
         <v>207000</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <f>SUM(E4:E4)</f>
         <v>284000</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <f>SUM(F4:F4)</f>
         <v>366000</v>
       </c>
@@ -2248,23 +2274,23 @@
       <c r="A7" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>450*Assumptions!B22</f>
         <v>54000</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>464*Assumptions!B23</f>
         <v>92800</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>478*Assumptions!B24</f>
         <v>143400</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>492*Assumptions!B25</f>
         <v>196800</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>507*Assumptions!B26</f>
         <v>253500</v>
       </c>
@@ -2273,23 +2299,23 @@
       <c r="A8" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <f>SUM(B7:B7)</f>
         <v>54000</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>SUM(C7:C7)</f>
         <v>92800</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>SUM(D7:D7)</f>
         <v>143400</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>SUM(E7:E7)</f>
         <v>196800</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>SUM(F7:F7)</f>
         <v>253500</v>
       </c>
@@ -2308,23 +2334,23 @@
       <c r="A10" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>22000*12</f>
         <v>264000</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>22660*12</f>
         <v>271920</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>23340*12</f>
         <v>280080</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>24040*12</f>
         <v>288480</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>24761*12</f>
         <v>297132</v>
       </c>
@@ -2333,23 +2359,23 @@
       <c r="A11" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>3000*12</f>
         <v>36000</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>3090*12</f>
         <v>37080</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>3183*12</f>
         <v>38196</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>3278*12</f>
         <v>39336</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>3377*12</f>
         <v>40524</v>
       </c>
@@ -2358,19 +2384,19 @@
       <c r="A12" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <v>22000</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <v>22660</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <v>23340</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <v>24040</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <v>24761</v>
       </c>
     </row>
@@ -2378,23 +2404,23 @@
       <c r="A13" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="28">
         <f>SUM(B10:B12)</f>
         <v>322000</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <f>SUM(C10:C12)</f>
         <v>331660</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <f>SUM(D10:D12)</f>
         <v>341616</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="28">
         <f>SUM(E10:E12)</f>
         <v>351856</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
         <f>SUM(F10:F12)</f>
         <v>362417</v>
       </c>
@@ -2413,19 +2439,19 @@
       <c r="A15" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <v>30000</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <v>30900</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <v>31827</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <v>32782</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="27">
         <v>33765</v>
       </c>
     </row>
@@ -2433,19 +2459,19 @@
       <c r="A16" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="27">
         <v>12000</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="27">
         <v>12360</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
         <v>12731</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <v>13113</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="27">
         <v>13506</v>
       </c>
     </row>
@@ -2453,19 +2479,19 @@
       <c r="A17" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="27">
         <v>18000</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <v>18540</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <v>19096</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <v>19669</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="27">
         <v>20259</v>
       </c>
     </row>
@@ -2473,23 +2499,23 @@
       <c r="A18" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="27">
         <f>750*Assumptions!B22</f>
         <v>90000</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <f>773*Assumptions!B23</f>
         <v>154600</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <f>796*Assumptions!B24</f>
         <v>238800</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <f>820*Assumptions!B25</f>
         <v>328000</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="27">
         <f>845*Assumptions!B26</f>
         <v>422500</v>
       </c>
@@ -2498,23 +2524,23 @@
       <c r="A19" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="28">
         <f>SUM(B15:B18)</f>
         <v>150000</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f>SUM(C15:C18)</f>
         <v>216400</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>SUM(D15:D18)</f>
         <v>302454</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>SUM(E15:E18)</f>
         <v>393564</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="28">
         <f>SUM(F15:F18)</f>
         <v>490030</v>
       </c>
@@ -2523,23 +2549,23 @@
       <c r="A21" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="28">
         <f>B5+B8+B13+B19</f>
         <v>604000</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <f>C5+C8+C13+C19</f>
         <v>774860</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>D5+D8+D13+D19</f>
         <v>994470</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>E5+E8+E13+E19</f>
         <v>1226220</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="28">
         <f>F5+F8+F13+F19</f>
         <v>1471947</v>
       </c>
@@ -2567,22 +2593,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2600,19 +2626,19 @@
       <c r="A3" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <v>46628.6108154935</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <v>46628.6108154935</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <v>46628.6108154935</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <v>46628.6108154935</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <v>46628.6108154935</v>
       </c>
     </row>
@@ -2620,19 +2646,19 @@
       <c r="A4" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <v>60000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>20000</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <v>25000</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>10000</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <v>10000</v>
       </c>
     </row>
@@ -2640,23 +2666,23 @@
       <c r="A5" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>SUM(B3:B4)</f>
         <v>106629</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <f>SUM(C3:C4)</f>
         <v>66629</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>SUM(D3:D4)</f>
         <v>71629</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <f>SUM(E3:E4)</f>
         <v>56629</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <f>SUM(F3:F4)</f>
         <v>56629</v>
       </c>
@@ -2684,22 +2710,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2707,23 +2733,23 @@
       <c r="A2" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="27">
         <f>'Revenue Schedule'!B16</f>
         <v>1465000</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="27">
         <f>'Revenue Schedule'!C16</f>
         <v>2328800</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="27">
         <f>'Revenue Schedule'!D16</f>
         <v>3452300</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="27">
         <f>'Revenue Schedule'!E16</f>
         <v>4623000</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="27">
         <f>'Revenue Schedule'!F16</f>
         <v>5891500</v>
       </c>
@@ -2732,23 +2758,23 @@
       <c r="A3" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>'Staffing &amp; Personnel'!B26</f>
         <v>780535</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <f>'Staffing &amp; Personnel'!C26</f>
         <v>936642</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>'Staffing &amp; Personnel'!D26</f>
         <v>936642</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f>'Staffing &amp; Personnel'!E26</f>
         <v>936642</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="27">
         <f>'Staffing &amp; Personnel'!F26</f>
         <v>936642</v>
       </c>
@@ -2757,23 +2783,23 @@
       <c r="A4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>'Operating Expenses'!B21</f>
         <v>604000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <f>'Operating Expenses'!C21</f>
         <v>774860</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <f>'Operating Expenses'!D21</f>
         <v>994470</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f>'Operating Expenses'!E21</f>
         <v>1226220</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <f>'Operating Expenses'!F21</f>
         <v>1471947</v>
       </c>
@@ -2782,23 +2808,23 @@
       <c r="A5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <f>'Capital &amp; Debt'!B5</f>
         <v>106629</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>'Capital &amp; Debt'!C5</f>
         <v>66629</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>'Capital &amp; Debt'!D5</f>
         <v>71629</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>'Capital &amp; Debt'!E5</f>
         <v>56629</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>'Capital &amp; Debt'!F5</f>
         <v>56629</v>
       </c>
@@ -2807,23 +2833,23 @@
       <c r="A6" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>B3+B4+B5</f>
         <v>1491164</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>C3+C4+C5</f>
         <v>1778131</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>D3+D4+D5</f>
         <v>2002741</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>E3+E4+E5</f>
         <v>2219491</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>F3+F4+F5</f>
         <v>2465218</v>
       </c>
@@ -2832,23 +2858,23 @@
       <c r="A7" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>B2-B6</f>
         <v>-26164</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>C2-C6</f>
         <v>550669</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>D2-D6</f>
         <v>1449559</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>E2-E6</f>
         <v>2403509</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <f>F2-F6</f>
         <v>3426282</v>
       </c>
@@ -2857,23 +2883,23 @@
       <c r="A8" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <f>B7</f>
         <v>-26164</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>B8+C7</f>
         <v>524505</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>C8+D7</f>
         <v>1974064</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>D8+E7</f>
         <v>4377573</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>E8+F7</f>
         <v>7803855</v>
       </c>
@@ -2882,23 +2908,23 @@
       <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34" t="str">
+      <c r="B9" s="36" t="str">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="36">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>3.5397054547724545</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="36">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>11.828173488234373</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="36">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>23.66798333491778</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="36">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>37.98700966811049</v>
       </c>
@@ -2926,17 +2952,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2954,7 +2980,7 @@
       <c r="A5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="33" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2962,7 +2988,7 @@
       <c r="A6" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="33" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2970,7 +2996,7 @@
       <c r="A7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="33" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2978,7 +3004,7 @@
       <c r="A8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="33" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2986,7 +3012,7 @@
       <c r="A9" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="33" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2994,7 +3020,7 @@
       <c r="A10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="33" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3002,7 +3028,7 @@
       <c r="A11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="33" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3010,7 +3036,7 @@
       <c r="A12" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="33" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3025,22 +3051,22 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3048,23 +3074,23 @@
       <c r="A16" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>'Revenue Schedule'!B2</f>
         <v>120</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>'Revenue Schedule'!C2</f>
         <v>200</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>'Revenue Schedule'!D2</f>
         <v>300</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>'Revenue Schedule'!E2</f>
         <v>400</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>'Revenue Schedule'!F2</f>
         <v>500</v>
       </c>
@@ -3076,40 +3102,40 @@
       <c r="B17" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="39">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="39">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="39">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="39">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3117,23 +3143,23 @@
       <c r="A20" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>'Financial Model'!B2</f>
         <v>1465000</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <f>'Financial Model'!C2</f>
         <v>2328800</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>'Financial Model'!D2</f>
         <v>3452300</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f>'Financial Model'!E2</f>
         <v>4623000</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>'Financial Model'!F2</f>
         <v>5891500</v>
       </c>
@@ -3142,23 +3168,23 @@
       <c r="A21" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>'Financial Model'!B3</f>
         <v>780535</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>'Financial Model'!C3</f>
         <v>936642</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>'Financial Model'!D3</f>
         <v>936642</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>'Financial Model'!E3</f>
         <v>936642</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <f>'Financial Model'!F3</f>
         <v>936642</v>
       </c>
@@ -3167,23 +3193,23 @@
       <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <f>'Financial Model'!B4</f>
         <v>604000</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>'Financial Model'!C4</f>
         <v>774860</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>'Financial Model'!D4</f>
         <v>994470</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f>'Financial Model'!E4</f>
         <v>1226220</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <f>'Financial Model'!F4</f>
         <v>1471947</v>
       </c>
@@ -3192,48 +3218,48 @@
       <c r="A23" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="28">
         <f>'Financial Model'!B6</f>
         <v>1491164</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="28">
         <f>'Financial Model'!C6</f>
         <v>1778131</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>'Financial Model'!D6</f>
         <v>2002741</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>'Financial Model'!E6</f>
         <v>2219491</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="28">
         <f>'Financial Model'!F6</f>
         <v>2465218</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="B24" s="38">
+      <c r="B24" s="40">
         <f>'Financial Model'!B7</f>
         <v>-26164</v>
       </c>
-      <c r="C24" s="39">
+      <c r="C24" s="41">
         <f>'Financial Model'!C7</f>
         <v>550669</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="41">
         <f>'Financial Model'!D7</f>
         <v>1449559</v>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="41">
         <f>'Financial Model'!E7</f>
         <v>2403509</v>
       </c>
-      <c r="F24" s="39">
+      <c r="F24" s="41">
         <f>'Financial Model'!F7</f>
         <v>3426282</v>
       </c>
@@ -3242,32 +3268,32 @@
       <c r="A25" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <f>'Financial Model'!B8</f>
         <v>-26164</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>'Financial Model'!C8</f>
         <v>524505</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <f>'Financial Model'!D8</f>
         <v>1974064</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <f>'Financial Model'!E8</f>
         <v>4377573</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="27">
         <f>'Financial Model'!F8</f>
         <v>7803855</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="40" t="str">
+      <c r="B26" s="42" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
@@ -3302,23 +3328,23 @@
       <c r="A29" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="27">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>12208.333333333334</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="27">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>11644</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="27">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>11507.666666666666</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="27">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>11557.5</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="27">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>11783</v>
       </c>
@@ -3327,23 +3353,23 @@
       <c r="A30" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="B30" s="37">
+      <c r="B30" s="39">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.5327883959044368</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="39">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.4021994160082446</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="39">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.2713095617414477</v>
       </c>
-      <c r="E30" s="37">
+      <c r="E30" s="39">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.20260480207657366</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="39">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.15898192310956463</v>
       </c>
@@ -3352,32 +3378,32 @@
       <c r="A31" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="39">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.41228668941979524</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="39">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.3327293026451391</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="39">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.2880601338238276</v>
       </c>
-      <c r="E31" s="37">
+      <c r="E31" s="39">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.26524334847501624</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="39">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.24984248493592465</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="B32" s="41">
+      <c r="B32" s="43">
         <f>IF(B20=0,0,B24/B20)</f>
         <v>-0.01785938566552901</v>
       </c>
@@ -3412,19 +3438,19 @@
       <c r="A35" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="39">
         <v>0.032764505119453925</v>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="39">
         <v>0.03538302988663689</v>
       </c>
-      <c r="D35" s="37">
+      <c r="D35" s="39">
         <v>0.03684500188280277</v>
       </c>
-      <c r="E35" s="37">
+      <c r="E35" s="39">
         <v>0.03781094527363184</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="39">
         <v>0.03819061359585844</v>
       </c>
     </row>
@@ -3432,19 +3458,19 @@
       <c r="A36" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="B36" s="37">
+      <c r="B36" s="39">
         <v>0.8477815699658703</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="39">
         <v>0.9066472002748196</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="39">
         <v>0.9356371114908901</v>
       </c>
-      <c r="E36" s="37">
+      <c r="E36" s="39">
         <v>0.9502920181700195</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F36" s="39">
         <v>0.9507765424764492</v>
       </c>
     </row>
@@ -3452,19 +3478,19 @@
       <c r="A37" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="39">
         <v>0.11945392491467577</v>
       </c>
-      <c r="C37" s="37">
+      <c r="C37" s="39">
         <v>0.057969769838543454</v>
       </c>
-      <c r="D37" s="37">
+      <c r="D37" s="39">
         <v>0.0275178866263071</v>
       </c>
-      <c r="E37" s="37">
+      <c r="E37" s="39">
         <v>0.01189703655634869</v>
       </c>
-      <c r="F37" s="37">
+      <c r="F37" s="39">
         <v>0.011032843927692439</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -105,6 +105,12 @@
     <t>SchoolStack Budget - Assumptions</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
     <t>SCHOOL INFORMATION</t>
   </si>
   <si>
@@ -223,9 +229,6 @@
   </si>
   <si>
     <t>5 Years</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Year 1</t>
@@ -525,7 +528,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -598,6 +601,12 @@
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -739,7 +748,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -759,33 +768,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1141,222 +1152,230 @@
       </c>
       <c r="B1" s="18"/>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>26</v>
+      <c r="A5" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>28</v>
+      <c r="A6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>30</v>
+      <c r="A7" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>32</v>
+      <c r="A8" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>34</v>
+      <c r="A9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="20">
+      <c r="A10" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="22">
         <v>2026</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="20">
+      <c r="A11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="20">
+      <c r="A12" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="22">
         <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>39</v>
+      <c r="A13" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="20">
+      <c r="A14" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="22">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>42</v>
+      <c r="A15" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>44</v>
+      <c r="A16" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>46</v>
+      <c r="A17" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>48</v>
+      <c r="A18" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>50</v>
+      <c r="A19" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" s="8"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="21">
+      <c r="A22" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="23">
         <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="21">
+      <c r="A23" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="23">
         <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="21">
+      <c r="A24" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="23">
         <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="21">
+      <c r="A25" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="23">
         <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="21">
+      <c r="A26" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="23">
         <v>500</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="22">
+      <c r="A29" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="22">
+      <c r="A30" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="23">
+      <c r="A31" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="25">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>62</v>
+      <c r="A32" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1385,53 +1404,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="28">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="28">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="28">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>Assumptions!B25</f>
         <v>400</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="28">
         <f>Assumptions!B26</f>
         <v>500</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1440,108 +1459,108 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="29">
         <f>8500*Assumptions!B22</f>
         <v>1020000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>8670*Assumptions!B23</f>
         <v>1734000</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>8843*Assumptions!B24</f>
         <v>2652900</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>9020*Assumptions!B25</f>
         <v>3608000</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>9200*Assumptions!B26</f>
         <v>4600000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="27">
+      <c r="A5" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="29">
         <f>750*Assumptions!B22</f>
         <v>90000</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>765*Assumptions!B23</f>
         <v>153000</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>780*Assumptions!B24</f>
         <v>234000</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <f>796*Assumptions!B25</f>
         <v>318400</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <f>812*Assumptions!B26</f>
         <v>406000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="27">
+      <c r="A6" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="29">
         <f>1100*Assumptions!B22</f>
         <v>132000</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="29">
         <f>1122*Assumptions!B23</f>
         <v>224400</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="29">
         <f>1144*Assumptions!B24</f>
         <v>343200</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="29">
         <f>1167*Assumptions!B25</f>
         <v>466800</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="29">
         <f>1191*Assumptions!B26</f>
         <v>595500</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="28">
+        <v>75</v>
+      </c>
+      <c r="B7" s="30">
         <f>SUM(B4:B6)</f>
         <v>1242000</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="30">
         <f>SUM(C4:C6)</f>
         <v>2111400</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="30">
         <f>SUM(D4:D6)</f>
         <v>3230100</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="30">
         <f>SUM(E4:E6)</f>
         <v>4393200</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="30">
         <f>SUM(F4:F6)</f>
         <v>5601500</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1550,73 +1569,73 @@
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="27">
+      <c r="A9" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="29">
         <v>150000</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="29">
         <v>100000</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="29">
         <v>50000</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="29">
         <v>0</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="A10" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="29">
         <v>25000</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="29">
         <v>35000</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="29">
         <v>45000</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="29">
         <v>55000</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="29">
         <v>65000</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="28" t="str">
+        <v>79</v>
+      </c>
+      <c r="B11" s="30" t="str">
         <f>SUM(B9:B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="28" t="str">
+      <c r="C11" s="30" t="str">
         <f>SUM(C9:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="28" t="str">
+      <c r="D11" s="30" t="str">
         <f>SUM(D9:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="28" t="str">
+      <c r="E11" s="30" t="str">
         <f>SUM(E9:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="28" t="str">
+      <c r="F11" s="30" t="str">
         <f>SUM(F9:F10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1625,76 +1644,76 @@
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="27">
+      <c r="A13" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="29">
         <f>400*Assumptions!B22</f>
         <v>48000</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="29">
         <f>412*Assumptions!B23</f>
         <v>82400</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="29">
         <f>424*Assumptions!B24</f>
         <v>127200</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="29">
         <f>437*Assumptions!B25</f>
         <v>174800</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="29">
         <f>450*Assumptions!B26</f>
         <v>225000</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="28">
+        <v>82</v>
+      </c>
+      <c r="B14" s="30">
         <f>SUM(B13:B13)</f>
         <v>48000</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="30">
         <f>SUM(C13:C13)</f>
         <v>82400</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="30">
         <f>SUM(D13:D13)</f>
         <v>127200</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="30">
         <f>SUM(E13:E13)</f>
         <v>174800</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="30">
         <f>SUM(F13:F13)</f>
         <v>225000</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="28">
+        <v>83</v>
+      </c>
+      <c r="B16" s="30">
         <f>B7+B11+B14</f>
         <v>1465000</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="30">
         <f>C7+C11+C14</f>
         <v>2328800</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="30">
         <f>D7+D11+D14</f>
         <v>3452300</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="30">
         <f>E7+E11+E14</f>
         <v>4623000</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="30">
         <f>F7+F11+F14</f>
         <v>5891500</v>
       </c>
@@ -1723,7 +1742,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1734,51 +1753,51 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="D3" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="F3" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="G3" s="27" t="s">
         <v>91</v>
       </c>
+      <c r="H3" s="27" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="29">
+      <c r="C4" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="25">
         <v>1</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>105000</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="24">
         <v>0.26</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="24">
         <v>0.0765</v>
       </c>
       <c r="H4" s="32">
@@ -1786,25 +1805,25 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="29">
+      <c r="D5" s="25">
         <v>1</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>82000</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="24">
         <v>0.26</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="24">
         <v>0.0765</v>
       </c>
       <c r="H5" s="32">
@@ -1812,25 +1831,25 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="A6" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="29">
+      <c r="B6" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="25">
         <v>5</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>50000</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="24">
         <v>0.26</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="24">
         <v>0.0765</v>
       </c>
       <c r="H6" s="32">
@@ -1838,25 +1857,25 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="29">
+      <c r="C7" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="25">
         <v>1</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>53000</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="24">
         <v>0.26</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="24">
         <v>0.0765</v>
       </c>
       <c r="H7" s="32">
@@ -1864,25 +1883,25 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="29">
+      <c r="A8" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="25">
         <v>3</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>28000</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="24">
         <v>0.18</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="24">
         <v>0.0765</v>
       </c>
       <c r="H8" s="32">
@@ -1890,25 +1909,25 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="29">
+      <c r="B9" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="25">
         <v>1</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>62000</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="24">
         <v>0.26</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="24">
         <v>0.0765</v>
       </c>
       <c r="H9" s="32">
@@ -1916,25 +1935,25 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="29">
+      <c r="B10" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="25">
         <v>2</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>36000</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="24">
         <v>0.22</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="24">
         <v>0.0765</v>
       </c>
       <c r="H10" s="32">
@@ -1943,7 +1962,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1954,64 +1973,64 @@
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>105</v>
+      <c r="A13" s="21" t="s">
+        <v>106</v>
       </c>
       <c r="B13" s="33">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>106</v>
+      <c r="A14" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="B14" s="33">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B15" s="30">
+      <c r="A15" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="34">
         <v>708000</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="30">
+      <c r="A16" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="34">
         <v>174480</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="30">
+      <c r="A17" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="34">
         <v>54162</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" s="30">
+      <c r="A18" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="32">
+        <v>112</v>
+      </c>
+      <c r="B19" s="35">
         <v>936642</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2020,112 +2039,112 @@
       <c r="F21" s="8"/>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="25" t="s">
+      <c r="A22" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="C22" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="D22" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="E22" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F22" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="27">
+      <c r="A23" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="29">
         <v>936642</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="29">
         <v>936642</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="29">
         <v>936642</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="29">
         <v>936642</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="29">
         <v>936642</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" s="34">
+      <c r="A24" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="36">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="36">
         <f>(1+Assumptions!B29)^1</f>
         <v>1</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="36">
         <f>(1+Assumptions!B29)^2</f>
         <v>1</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="36">
         <f>(1+Assumptions!B29)^3</f>
         <v>1</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="36">
         <f>(1+Assumptions!B29)^4</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B25" s="35">
+      <c r="A25" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="37">
         <f>Assumptions!B31</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="37">
         <v>1</v>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="37">
         <v>1</v>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="37">
         <v>1</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="37">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B26" s="28">
+        <v>117</v>
+      </c>
+      <c r="B26" s="30">
         <f>B23*B24*B25</f>
         <v>780535</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="30">
         <f>C23*C24*C25</f>
         <v>936642</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="30">
         <f>D23*D24*D25</f>
         <v>936642</v>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="30">
         <f>E23*E24*E25</f>
         <v>936642</v>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="30">
         <f>F23*F24*F25</f>
         <v>936642</v>
       </c>
@@ -2156,53 +2175,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="28">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="28">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="28">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>Assumptions!B25</f>
         <v>400</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="28">
         <f>Assumptions!B26</f>
         <v>500</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2211,58 +2230,58 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="29">
         <f>650*Assumptions!B22</f>
         <v>78000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>670*Assumptions!B23</f>
         <v>134000</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>690*Assumptions!B24</f>
         <v>207000</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>710*Assumptions!B25</f>
         <v>284000</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>732*Assumptions!B26</f>
         <v>366000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="28">
+        <v>120</v>
+      </c>
+      <c r="B5" s="30">
         <f>SUM(B4:B4)</f>
         <v>78000</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="30">
         <f>SUM(C4:C4)</f>
         <v>134000</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="30">
         <f>SUM(D4:D4)</f>
         <v>207000</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="30">
         <f>SUM(E4:E4)</f>
         <v>284000</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="30">
         <f>SUM(F4:F4)</f>
         <v>366000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2271,58 +2290,58 @@
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="27">
+      <c r="A7" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="29">
         <f>450*Assumptions!B22</f>
         <v>54000</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="29">
         <f>464*Assumptions!B23</f>
         <v>92800</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="29">
         <f>478*Assumptions!B24</f>
         <v>143400</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="29">
         <f>492*Assumptions!B25</f>
         <v>196800</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="29">
         <f>507*Assumptions!B26</f>
         <v>253500</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B8" s="28">
+        <v>123</v>
+      </c>
+      <c r="B8" s="30">
         <f>SUM(B7:B7)</f>
         <v>54000</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="30">
         <f>SUM(C7:C7)</f>
         <v>92800</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="30">
         <f>SUM(D7:D7)</f>
         <v>143400</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="30">
         <f>SUM(E7:E7)</f>
         <v>196800</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="30">
         <f>SUM(F7:F7)</f>
         <v>253500</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2331,103 +2350,103 @@
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="A10" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="29">
         <f>22000*12</f>
         <v>264000</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="29">
         <f>22660*12</f>
         <v>271920</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="29">
         <f>23340*12</f>
         <v>280080</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="29">
         <f>24040*12</f>
         <v>288480</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="29">
         <f>24761*12</f>
         <v>297132</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="29">
         <f>3000*12</f>
         <v>36000</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="29">
         <f>3090*12</f>
         <v>37080</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="29">
         <f>3183*12</f>
         <v>38196</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="29">
         <f>3278*12</f>
         <v>39336</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="29">
         <f>3377*12</f>
         <v>40524</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="27">
+      <c r="A12" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="29">
         <v>22000</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="29">
         <v>22660</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="29">
         <v>23340</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="29">
         <v>24040</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="29">
         <v>24761</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="28">
+        <v>128</v>
+      </c>
+      <c r="B13" s="30">
         <f>SUM(B10:B12)</f>
         <v>322000</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="30">
         <f>SUM(C10:C12)</f>
         <v>331660</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="30">
         <f>SUM(D10:D12)</f>
         <v>341616</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="30">
         <f>SUM(E10:E12)</f>
         <v>351856</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="30">
         <f>SUM(F10:F12)</f>
         <v>362417</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2436,136 +2455,136 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="27">
+      <c r="A15" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="29">
         <v>30000</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="29">
         <v>30900</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="29">
         <v>31827</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="29">
         <v>32782</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="29">
         <v>33765</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="B16" s="27">
+      <c r="A16" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="29">
         <v>12000</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="29">
         <v>12360</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="29">
         <v>12731</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="29">
         <v>13113</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="29">
         <v>13506</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="B17" s="27">
+      <c r="A17" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="29">
         <v>18000</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="29">
         <v>18540</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="29">
         <v>19096</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="29">
         <v>19669</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="29">
         <v>20259</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B18" s="27">
+      <c r="A18" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="29">
         <f>750*Assumptions!B22</f>
         <v>90000</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="29">
         <f>773*Assumptions!B23</f>
         <v>154600</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="29">
         <f>796*Assumptions!B24</f>
         <v>238800</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="29">
         <f>820*Assumptions!B25</f>
         <v>328000</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="29">
         <f>845*Assumptions!B26</f>
         <v>422500</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B19" s="28">
+        <v>134</v>
+      </c>
+      <c r="B19" s="30">
         <f>SUM(B15:B18)</f>
         <v>150000</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="30">
         <f>SUM(C15:C18)</f>
         <v>216400</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="30">
         <f>SUM(D15:D18)</f>
         <v>302454</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="30">
         <f>SUM(E15:E18)</f>
         <v>393564</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="30">
         <f>SUM(F15:F18)</f>
         <v>490030</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="28">
+        <v>135</v>
+      </c>
+      <c r="B21" s="30">
         <f>B5+B8+B13+B19</f>
         <v>604000</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="30">
         <f>C5+C8+C13+C19</f>
         <v>774860</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="30">
         <f>D5+D8+D13+D19</f>
         <v>994470</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="30">
         <f>E5+E8+E13+E19</f>
         <v>1226220</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="30">
         <f>F5+F8+F13+F19</f>
         <v>1471947</v>
       </c>
@@ -2593,28 +2612,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="A1" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2623,66 +2642,66 @@
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="29">
         <v>46628.6108154935</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="29">
         <v>46628.6108154935</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <v>46628.6108154935</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="29">
         <v>46628.6108154935</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="29">
         <v>46628.6108154935</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4" s="27">
+      <c r="A4" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="29">
         <v>60000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <v>20000</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <v>25000</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <v>10000</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <v>10000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="28">
+        <v>139</v>
+      </c>
+      <c r="B5" s="30">
         <f>SUM(B3:B4)</f>
         <v>106629</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="30">
         <f>SUM(C3:C4)</f>
         <v>66629</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="30">
         <f>SUM(D3:D4)</f>
         <v>71629</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="30">
         <f>SUM(E3:E4)</f>
         <v>56629</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="30">
         <f>SUM(F3:F4)</f>
         <v>56629</v>
       </c>
@@ -2710,221 +2729,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="25" t="s">
+      <c r="B1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F1" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="27">
+      <c r="A2" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="29">
         <f>'Revenue Schedule'!B16</f>
         <v>1465000</v>
       </c>
-      <c r="C2" s="27">
+      <c r="C2" s="29">
         <f>'Revenue Schedule'!C16</f>
         <v>2328800</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="29">
         <f>'Revenue Schedule'!D16</f>
         <v>3452300</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="29">
         <f>'Revenue Schedule'!E16</f>
         <v>4623000</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="29">
         <f>'Revenue Schedule'!F16</f>
         <v>5891500</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="27">
+      <c r="A3" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="29">
         <f>'Staffing &amp; Personnel'!B26</f>
         <v>780535</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="29">
         <f>'Staffing &amp; Personnel'!C26</f>
         <v>936642</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="29">
         <f>'Staffing &amp; Personnel'!D26</f>
         <v>936642</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="29">
         <f>'Staffing &amp; Personnel'!E26</f>
         <v>936642</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="29">
         <f>'Staffing &amp; Personnel'!F26</f>
         <v>936642</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="29">
         <f>'Operating Expenses'!B21</f>
         <v>604000</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="29">
         <f>'Operating Expenses'!C21</f>
         <v>774860</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <f>'Operating Expenses'!D21</f>
         <v>994470</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <f>'Operating Expenses'!E21</f>
         <v>1226220</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <f>'Operating Expenses'!F21</f>
         <v>1471947</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="29">
         <f>'Capital &amp; Debt'!B5</f>
         <v>106629</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>'Capital &amp; Debt'!C5</f>
         <v>66629</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>'Capital &amp; Debt'!D5</f>
         <v>71629</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <f>'Capital &amp; Debt'!E5</f>
         <v>56629</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <f>'Capital &amp; Debt'!F5</f>
         <v>56629</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B6" s="28">
+        <v>142</v>
+      </c>
+      <c r="B6" s="30">
         <f>B3+B4+B5</f>
         <v>1491164</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="30">
         <f>C3+C4+C5</f>
         <v>1778131</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="30">
         <f>D3+D4+D5</f>
         <v>2002741</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f>E3+E4+E5</f>
         <v>2219491</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="30">
         <f>F3+F4+F5</f>
         <v>2465218</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" s="28">
+        <v>143</v>
+      </c>
+      <c r="B7" s="30">
         <f>B2-B6</f>
         <v>-26164</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="30">
         <f>C2-C6</f>
         <v>550669</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="30">
         <f>D2-D6</f>
         <v>1449559</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="30">
         <f>E2-E6</f>
         <v>2403509</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="30">
         <f>F2-F6</f>
         <v>3426282</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="A8" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="29">
         <f>B7</f>
         <v>-26164</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="29">
         <f>B8+C7</f>
         <v>524505</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <f>C8+D7</f>
         <v>1974064</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="29">
         <f>D8+E7</f>
         <v>4377573</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="29">
         <f>E8+F7</f>
         <v>7803855</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="36" t="str">
+      <c r="B9" s="38" t="str">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="38">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>3.5397054547724545</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="38">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>11.828173488234373</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="38">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>23.66798333491778</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="38">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>37.98700966811049</v>
       </c>
@@ -2952,23 +2971,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="A1" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>145</v>
+      <c r="A2" s="40" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2977,72 +2996,72 @@
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>24</v>
+      <c r="A5" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B10" s="33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>38</v>
+      <c r="A11" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="B11" s="33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>37</v>
-      </c>
       <c r="B12" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3051,240 +3070,240 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="25" t="s">
+      <c r="A15" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="C15" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="D15" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="E15" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F15" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="26">
+      <c r="A16" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="28">
         <f>'Revenue Schedule'!B2</f>
         <v>120</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="28">
         <f>'Revenue Schedule'!C2</f>
         <v>200</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="28">
         <f>'Revenue Schedule'!D2</f>
         <v>300</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="28">
         <f>'Revenue Schedule'!E2</f>
         <v>400</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="28">
         <f>'Revenue Schedule'!F2</f>
         <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>148</v>
+      <c r="A17" s="21" t="s">
+        <v>149</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" s="39">
+        <v>150</v>
+      </c>
+      <c r="C17" s="41">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="41">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="41">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="41">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="25" t="s">
+      <c r="A19" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="C19" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="D19" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="E19" s="27" t="s">
         <v>68</v>
       </c>
+      <c r="F19" s="27" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" s="27">
+      <c r="A20" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="29">
         <f>'Financial Model'!B2</f>
         <v>1465000</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="29">
         <f>'Financial Model'!C2</f>
         <v>2328800</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="29">
         <f>'Financial Model'!D2</f>
         <v>3452300</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="29">
         <f>'Financial Model'!E2</f>
         <v>4623000</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="29">
         <f>'Financial Model'!F2</f>
         <v>5891500</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="B21" s="27">
+      <c r="A21" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="29">
         <f>'Financial Model'!B3</f>
         <v>780535</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="29">
         <f>'Financial Model'!C3</f>
         <v>936642</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="29">
         <f>'Financial Model'!D3</f>
         <v>936642</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="29">
         <f>'Financial Model'!E3</f>
         <v>936642</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="29">
         <f>'Financial Model'!F3</f>
         <v>936642</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="29">
         <f>'Financial Model'!B4</f>
         <v>604000</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="29">
         <f>'Financial Model'!C4</f>
         <v>774860</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="29">
         <f>'Financial Model'!D4</f>
         <v>994470</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="29">
         <f>'Financial Model'!E4</f>
         <v>1226220</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="29">
         <f>'Financial Model'!F4</f>
         <v>1471947</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="28">
+        <v>142</v>
+      </c>
+      <c r="B23" s="30">
         <f>'Financial Model'!B6</f>
         <v>1491164</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="30">
         <f>'Financial Model'!C6</f>
         <v>1778131</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="30">
         <f>'Financial Model'!D6</f>
         <v>2002741</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="30">
         <f>'Financial Model'!E6</f>
         <v>2219491</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="30">
         <f>'Financial Model'!F6</f>
         <v>2465218</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="B24" s="40">
+        <v>143</v>
+      </c>
+      <c r="B24" s="42">
         <f>'Financial Model'!B7</f>
         <v>-26164</v>
       </c>
-      <c r="C24" s="41">
+      <c r="C24" s="43">
         <f>'Financial Model'!C7</f>
         <v>550669</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="43">
         <f>'Financial Model'!D7</f>
         <v>1449559</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="43">
         <f>'Financial Model'!E7</f>
         <v>2403509</v>
       </c>
-      <c r="F24" s="41">
+      <c r="F24" s="43">
         <f>'Financial Model'!F7</f>
         <v>3426282</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="B25" s="27">
+      <c r="A25" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="29">
         <f>'Financial Model'!B8</f>
         <v>-26164</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="29">
         <f>'Financial Model'!C8</f>
         <v>524505</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="29">
         <f>'Financial Model'!D8</f>
         <v>1974064</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="29">
         <f>'Financial Model'!E8</f>
         <v>4377573</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="29">
         <f>'Financial Model'!F8</f>
         <v>7803855</v>
       </c>
@@ -3293,7 +3312,7 @@
       <c r="A26" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="42" t="str">
+      <c r="B26" s="44" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
@@ -3316,7 +3335,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3325,85 +3344,85 @@
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B29" s="27">
+      <c r="A29" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B29" s="29">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>12208.333333333334</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="29">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>11644</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="29">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>11507.666666666666</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="29">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>11557.5</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="29">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>11783</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="B30" s="39">
+      <c r="A30" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="41">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.5327883959044368</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="41">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.4021994160082446</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="41">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.2713095617414477</v>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="41">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.20260480207657366</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F30" s="41">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.15898192310956463</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B31" s="39">
+      <c r="A31" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" s="41">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.41228668941979524</v>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="41">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.3327293026451391</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="41">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.2880601338238276</v>
       </c>
-      <c r="E31" s="39">
+      <c r="E31" s="41">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.26524334847501624</v>
       </c>
-      <c r="F31" s="39">
+      <c r="F31" s="41">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.24984248493592465</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="B32" s="43">
+        <v>155</v>
+      </c>
+      <c r="B32" s="45">
         <f>IF(B20=0,0,B24/B20)</f>
         <v>-0.01785938566552901</v>
       </c>
@@ -3426,7 +3445,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3435,62 +3454,62 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="B35" s="39">
+      <c r="A35" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35" s="41">
         <v>0.032764505119453925</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="41">
         <v>0.03538302988663689</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="41">
         <v>0.03684500188280277</v>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="41">
         <v>0.03781094527363184</v>
       </c>
-      <c r="F35" s="39">
+      <c r="F35" s="41">
         <v>0.03819061359585844</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B36" s="39">
+      <c r="A36" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" s="41">
         <v>0.8477815699658703</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="41">
         <v>0.9066472002748196</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="41">
         <v>0.9356371114908901</v>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="41">
         <v>0.9502920181700195</v>
       </c>
-      <c r="F36" s="39">
+      <c r="F36" s="41">
         <v>0.9507765424764492</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="B37" s="39">
+      <c r="A37" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37" s="41">
         <v>0.11945392491467577</v>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="41">
         <v>0.057969769838543454</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="41">
         <v>0.0275178866263071</v>
       </c>
-      <c r="E37" s="39">
+      <c r="E37" s="41">
         <v>0.01189703655634869</v>
       </c>
-      <c r="F37" s="39">
+      <c r="F37" s="41">
         <v>0.011032843927692439</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -14,7 +14,7 @@
     <sheet sheetId="7" name="Summary" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$B32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="161">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -650,7 +653,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -674,6 +677,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
@@ -688,7 +696,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -730,6 +738,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
@@ -748,7 +765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -770,13 +787,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -793,10 +811,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="20" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1139,7 +1157,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1152,230 +1170,236 @@
       </c>
       <c r="B1" s="18"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>24</v>
       </c>
+      <c r="D2" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="22" t="s">
+      <c r="A5" s="22" t="s">
         <v>28</v>
       </c>
+      <c r="B5" s="23" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="22" t="s">
+      <c r="A6" s="22" t="s">
         <v>30</v>
       </c>
+      <c r="B6" s="23" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="22" t="s">
+      <c r="A7" s="22" t="s">
         <v>32</v>
       </c>
+      <c r="B7" s="23" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="22" t="s">
+      <c r="A8" s="22" t="s">
         <v>34</v>
       </c>
+      <c r="B8" s="23" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="22" t="s">
+      <c r="A9" s="22" t="s">
         <v>36</v>
       </c>
+      <c r="B9" s="23" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="A10" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="23">
         <v>2026</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="A11" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="22">
+      <c r="A12" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="23">
         <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="22" t="s">
+      <c r="A13" s="22" t="s">
         <v>41</v>
       </c>
+      <c r="B13" s="23" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="22">
+      <c r="A14" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="22" t="s">
         <v>44</v>
       </c>
+      <c r="B15" s="23" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="22" t="s">
         <v>46</v>
       </c>
+      <c r="B16" s="23" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="22" t="s">
         <v>48</v>
       </c>
+      <c r="B17" s="23" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="22" t="s">
         <v>50</v>
       </c>
+      <c r="B18" s="23" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="22" t="s">
+      <c r="A19" s="22" t="s">
         <v>52</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="8"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="23">
+      <c r="A22" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="24">
         <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="23">
+      <c r="A23" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="24">
         <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="23">
+      <c r="A24" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="24">
         <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="23">
+      <c r="A25" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="24">
         <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="23">
+      <c r="A26" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="24">
         <v>500</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="8"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="24">
+      <c r="A29" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="24">
+      <c r="A30" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="25">
+      <c r="A31" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="26">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="26" t="s">
+      <c r="A32" s="22" t="s">
         <v>64</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1404,53 +1428,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="28">
+      <c r="A2" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="29">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <f>Assumptions!B25</f>
         <v>400</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>500</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1459,108 +1483,108 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="30">
         <f>8500*Assumptions!B22</f>
         <v>1020000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>8670*Assumptions!B23</f>
         <v>1734000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>8843*Assumptions!B24</f>
         <v>2652900</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>9020*Assumptions!B25</f>
         <v>3608000</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>9200*Assumptions!B26</f>
         <v>4600000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="A5" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="30">
         <f>750*Assumptions!B22</f>
         <v>90000</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>765*Assumptions!B23</f>
         <v>153000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>780*Assumptions!B24</f>
         <v>234000</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>796*Assumptions!B25</f>
         <v>318400</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>812*Assumptions!B26</f>
         <v>406000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="29">
+      <c r="A6" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="30">
         <f>1100*Assumptions!B22</f>
         <v>132000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <f>1122*Assumptions!B23</f>
         <v>224400</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>1144*Assumptions!B24</f>
         <v>343200</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <f>1167*Assumptions!B25</f>
         <v>466800</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <f>1191*Assumptions!B26</f>
         <v>595500</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="30">
+        <v>76</v>
+      </c>
+      <c r="B7" s="31">
         <f>SUM(B4:B6)</f>
         <v>1242000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>SUM(C4:C6)</f>
         <v>2111400</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>SUM(D4:D6)</f>
         <v>3230100</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>SUM(E4:E6)</f>
         <v>4393200</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>SUM(F4:F6)</f>
         <v>5601500</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1569,73 +1593,73 @@
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="29">
+      <c r="A9" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="30">
         <v>150000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>100000</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>50000</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>0</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="29">
+      <c r="A10" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="30">
         <v>25000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>35000</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>45000</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>55000</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>65000</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="30" t="str">
+        <v>80</v>
+      </c>
+      <c r="B11" s="31" t="str">
         <f>SUM(B9:B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="30" t="str">
+      <c r="C11" s="31" t="str">
         <f>SUM(C9:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="30" t="str">
+      <c r="D11" s="31" t="str">
         <f>SUM(D9:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="30" t="str">
+      <c r="E11" s="31" t="str">
         <f>SUM(E9:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="30" t="str">
+      <c r="F11" s="31" t="str">
         <f>SUM(F9:F10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1644,76 +1668,76 @@
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="29">
+      <c r="A13" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="30">
         <f>400*Assumptions!B22</f>
         <v>48000</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>412*Assumptions!B23</f>
         <v>82400</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>424*Assumptions!B24</f>
         <v>127200</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>437*Assumptions!B25</f>
         <v>174800</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>450*Assumptions!B26</f>
         <v>225000</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="30">
+        <v>83</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B13:B13)</f>
         <v>48000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>SUM(C13:C13)</f>
         <v>82400</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>SUM(D13:D13)</f>
         <v>127200</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>SUM(E13:E13)</f>
         <v>174800</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>SUM(F13:F13)</f>
         <v>225000</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="30">
+        <v>84</v>
+      </c>
+      <c r="B16" s="31">
         <f>B7+B11+B14</f>
         <v>1465000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>C7+C11+C14</f>
         <v>2328800</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <f>D7+D11+D14</f>
         <v>3452300</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <f>E7+E11+E14</f>
         <v>4623000</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f>F7+F11+F14</f>
         <v>5891500</v>
       </c>
@@ -1742,7 +1766,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1753,216 +1777,216 @@
       <c r="H1" s="18"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="27" t="s">
+      <c r="A3" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="C3" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="D3" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="E3" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="G3" s="28" t="s">
         <v>92</v>
       </c>
+      <c r="H3" s="28" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="25">
+      <c r="C4" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="26">
         <v>1</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <v>105000</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="25">
         <v>0.26</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="33">
         <v>140332.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>1</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <v>82000</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>0.26</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="33">
         <v>109593</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="25">
+      <c r="B6" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="26">
         <v>5</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <v>50000</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>0.26</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="33">
         <v>334125</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="25">
+      <c r="C7" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="26">
         <v>1</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <v>53000</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>0.26</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="33">
         <v>70834.5</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="A8" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="26">
         <v>3</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <v>28000</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>0.18</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="33">
         <v>105546</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="25">
+      <c r="B9" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="26">
         <v>1</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <v>62000</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>0.26</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="33">
         <v>82863</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="25">
+      <c r="B10" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="26">
         <v>2</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <v>36000</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>0.22</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="25">
         <v>0.0765</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="33">
         <v>93348</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1973,64 +1997,64 @@
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="33">
+      <c r="A13" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="34">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="33">
+      <c r="A14" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="34">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="34">
+      <c r="A15" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="35">
         <v>708000</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="B16" s="34">
+      <c r="A16" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="35">
         <v>174480</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" s="34">
+      <c r="A17" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="35">
         <v>54162</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="34">
+      <c r="A18" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="35">
+      <c r="A19" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="36">
         <v>936642</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2039,112 +2063,112 @@
       <c r="F21" s="8"/>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="27" t="s">
+      <c r="B22" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="C22" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="D22" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="E22" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F22" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="A23" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="30">
         <v>936642</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <v>936642</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <v>936642</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <v>936642</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <v>936642</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B24" s="36">
+      <c r="A24" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="37">
         <f>(1+Assumptions!B29)^0</f>
         <v>1</v>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="37">
         <f>(1+Assumptions!B29)^1</f>
         <v>1</v>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="37">
         <f>(1+Assumptions!B29)^2</f>
         <v>1</v>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="37">
         <f>(1+Assumptions!B29)^3</f>
         <v>1</v>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="37">
         <f>(1+Assumptions!B29)^4</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" s="37">
+      <c r="A25" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="38">
         <f>Assumptions!B31</f>
         <v>0.8333333333333334</v>
       </c>
-      <c r="C25" s="37">
+      <c r="C25" s="38">
         <v>1</v>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="38">
         <v>1</v>
       </c>
-      <c r="E25" s="37">
+      <c r="E25" s="38">
         <v>1</v>
       </c>
-      <c r="F25" s="37">
+      <c r="F25" s="38">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" s="30">
+        <v>118</v>
+      </c>
+      <c r="B26" s="31">
         <f>B23*B24*B25</f>
         <v>780535</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <f>C23*C24*C25</f>
         <v>936642</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <f>D23*D24*D25</f>
         <v>936642</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="31">
         <f>E23*E24*E25</f>
         <v>936642</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="31">
         <f>F23*F24*F25</f>
         <v>936642</v>
       </c>
@@ -2175,53 +2199,53 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="28">
+      <c r="A2" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="29">
         <f>Assumptions!B22</f>
         <v>120</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <f>Assumptions!B23</f>
         <v>200</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <f>Assumptions!B24</f>
         <v>300</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <f>Assumptions!B25</f>
         <v>400</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <f>Assumptions!B26</f>
         <v>500</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2230,58 +2254,58 @@
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="30">
         <f>650*Assumptions!B22</f>
         <v>78000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>670*Assumptions!B23</f>
         <v>134000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>690*Assumptions!B24</f>
         <v>207000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>710*Assumptions!B25</f>
         <v>284000</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>732*Assumptions!B26</f>
         <v>366000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="30">
+        <v>121</v>
+      </c>
+      <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
         <v>78000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>SUM(C4:C4)</f>
         <v>134000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>SUM(D4:D4)</f>
         <v>207000</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>SUM(E4:E4)</f>
         <v>284000</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>SUM(F4:F4)</f>
         <v>366000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2290,58 +2314,58 @@
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="29">
+      <c r="A7" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="30">
         <f>450*Assumptions!B22</f>
         <v>54000</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>464*Assumptions!B23</f>
         <v>92800</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>478*Assumptions!B24</f>
         <v>143400</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>492*Assumptions!B25</f>
         <v>196800</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>507*Assumptions!B26</f>
         <v>253500</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="30">
+        <v>124</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
         <v>54000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C7:C7)</f>
         <v>92800</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D7:D7)</f>
         <v>143400</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E7:E7)</f>
         <v>196800</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F7:F7)</f>
         <v>253500</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2350,103 +2374,103 @@
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="29">
+      <c r="A10" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="30">
         <f>22000*12</f>
         <v>264000</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>22660*12</f>
         <v>271920</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>23340*12</f>
         <v>280080</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>24040*12</f>
         <v>288480</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>24761*12</f>
         <v>297132</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="29">
+      <c r="A11" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="30">
         <f>3000*12</f>
         <v>36000</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>3090*12</f>
         <v>37080</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>3183*12</f>
         <v>38196</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>3278*12</f>
         <v>39336</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>3377*12</f>
         <v>40524</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="29">
+      <c r="A12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="30">
         <v>22000</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>22660</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>23340</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>24040</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>24761</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="30">
+        <v>129</v>
+      </c>
+      <c r="B13" s="31">
         <f>SUM(B10:B12)</f>
         <v>322000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>SUM(C10:C12)</f>
         <v>331660</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>SUM(D10:D12)</f>
         <v>341616</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>SUM(E10:E12)</f>
         <v>351856</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>SUM(F10:F12)</f>
         <v>362417</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2455,136 +2479,136 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="A15" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="30">
         <v>30000</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>30900</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>31827</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>32782</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>33765</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="29">
+      <c r="A16" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="30">
         <v>12000</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>12360</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>12731</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>13113</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>13506</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="29">
+      <c r="A17" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="30">
         <v>18000</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>18540</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>19096</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <v>19669</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <v>20259</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="29">
+      <c r="A18" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="30">
         <f>750*Assumptions!B22</f>
         <v>90000</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>773*Assumptions!B23</f>
         <v>154600</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>796*Assumptions!B24</f>
         <v>238800</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>820*Assumptions!B25</f>
         <v>328000</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <f>845*Assumptions!B26</f>
         <v>422500</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="30">
+        <v>135</v>
+      </c>
+      <c r="B19" s="31">
         <f>SUM(B15:B18)</f>
         <v>150000</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>SUM(C15:C18)</f>
         <v>216400</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>SUM(D15:D18)</f>
         <v>302454</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>SUM(E15:E18)</f>
         <v>393564</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>SUM(F15:F18)</f>
         <v>490030</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B21" s="30">
+        <v>136</v>
+      </c>
+      <c r="B21" s="31">
         <f>B5+B8+B13+B19</f>
         <v>604000</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>C5+C8+C13+C19</f>
         <v>774860</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <f>D5+D8+D13+D19</f>
         <v>994470</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <f>E5+E8+E13+E19</f>
         <v>1226220</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <f>F5+F8+F13+F19</f>
         <v>1471947</v>
       </c>
@@ -2612,28 +2636,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2642,66 +2666,66 @@
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="29">
+      <c r="A3" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="30">
         <v>46628.6108154935</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <v>46628.6108154935</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="30">
         <v>46628.6108154935</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="30">
         <v>46628.6108154935</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="30">
         <v>46628.6108154935</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="29">
+      <c r="A4" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="30">
         <v>60000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <v>20000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>25000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>10000</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <v>10000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="30">
+        <v>140</v>
+      </c>
+      <c r="B5" s="31">
         <f>SUM(B3:B4)</f>
         <v>106629</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>SUM(C3:C4)</f>
         <v>66629</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>SUM(D3:D4)</f>
         <v>71629</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>SUM(E3:E4)</f>
         <v>56629</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>SUM(F3:F4)</f>
         <v>56629</v>
       </c>
@@ -2729,221 +2753,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F1" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="B2" s="29">
+      <c r="A2" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="30">
         <f>'Revenue Schedule'!B16</f>
         <v>1465000</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="30">
         <f>'Revenue Schedule'!C16</f>
         <v>2328800</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="30">
         <f>'Revenue Schedule'!D16</f>
         <v>3452300</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="30">
         <f>'Revenue Schedule'!E16</f>
         <v>4623000</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="30">
         <f>'Revenue Schedule'!F16</f>
         <v>5891500</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="29">
+      <c r="A3" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B26</f>
         <v>780535</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <f>'Staffing &amp; Personnel'!C26</f>
         <v>936642</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="30">
         <f>'Staffing &amp; Personnel'!D26</f>
         <v>936642</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="30">
         <f>'Staffing &amp; Personnel'!E26</f>
         <v>936642</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="30">
         <f>'Staffing &amp; Personnel'!F26</f>
         <v>936642</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <f>'Operating Expenses'!B21</f>
         <v>604000</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <f>'Operating Expenses'!C21</f>
         <v>774860</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>'Operating Expenses'!D21</f>
         <v>994470</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>'Operating Expenses'!E21</f>
         <v>1226220</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>'Operating Expenses'!F21</f>
         <v>1471947</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <f>'Capital &amp; Debt'!B5</f>
         <v>106629</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <f>'Capital &amp; Debt'!C5</f>
         <v>66629</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <f>'Capital &amp; Debt'!D5</f>
         <v>71629</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>'Capital &amp; Debt'!E5</f>
         <v>56629</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>'Capital &amp; Debt'!F5</f>
         <v>56629</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="30">
+        <v>143</v>
+      </c>
+      <c r="B6" s="31">
         <f>B3+B4+B5</f>
         <v>1491164</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>C3+C4+C5</f>
         <v>1778131</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>D3+D4+D5</f>
         <v>2002741</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>E3+E4+E5</f>
         <v>2219491</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>F3+F4+F5</f>
         <v>2465218</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B7" s="30">
+        <v>144</v>
+      </c>
+      <c r="B7" s="31">
         <f>B2-B6</f>
         <v>-26164</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>C2-C6</f>
         <v>550669</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>D2-D6</f>
         <v>1449559</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>E2-E6</f>
         <v>2403509</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>F2-F6</f>
         <v>3426282</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" s="29">
+      <c r="A8" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="30">
         <f>B7</f>
         <v>-26164</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>B8+C7</f>
         <v>524505</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>C8+D7</f>
         <v>1974064</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>D8+E7</f>
         <v>4377573</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>E8+F7</f>
         <v>7803855</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="38" t="str">
+      <c r="B9" s="39" t="str">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="39">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>3.5397054547724545</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="39">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>11.828173488234373</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="39">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>23.66798333491778</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="39">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>37.98700966811049</v>
       </c>
@@ -2971,23 +2995,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="A1" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
-        <v>146</v>
+      <c r="A2" s="41" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2996,72 +3020,72 @@
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>147</v>
+      <c r="B12" s="34" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3070,249 +3094,249 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="C15" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="D15" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="E15" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F15" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="28">
+      <c r="A16" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="29">
         <f>'Revenue Schedule'!B2</f>
         <v>120</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>'Revenue Schedule'!C2</f>
         <v>200</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>'Revenue Schedule'!D2</f>
         <v>300</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>'Revenue Schedule'!E2</f>
         <v>400</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>'Revenue Schedule'!F2</f>
         <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>149</v>
+      <c r="A17" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" s="41">
+        <v>151</v>
+      </c>
+      <c r="C17" s="42">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="42">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="C19" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="D19" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="E19" s="28" t="s">
         <v>69</v>
       </c>
+      <c r="F19" s="28" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="B20" s="29">
+      <c r="A20" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="30">
         <f>'Financial Model'!B2</f>
         <v>1465000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>'Financial Model'!C2</f>
         <v>2328800</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>'Financial Model'!D2</f>
         <v>3452300</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>'Financial Model'!E2</f>
         <v>4623000</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f>'Financial Model'!F2</f>
         <v>5891500</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="30">
         <f>'Financial Model'!B3</f>
         <v>780535</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <f>'Financial Model'!C3</f>
         <v>936642</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <f>'Financial Model'!D3</f>
         <v>936642</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <f>'Financial Model'!E3</f>
         <v>936642</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <f>'Financial Model'!F3</f>
         <v>936642</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <f>'Financial Model'!B4</f>
         <v>604000</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>'Financial Model'!C4</f>
         <v>774860</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <f>'Financial Model'!D4</f>
         <v>994470</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <f>'Financial Model'!E4</f>
         <v>1226220</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <f>'Financial Model'!F4</f>
         <v>1471947</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B23" s="30">
+        <v>143</v>
+      </c>
+      <c r="B23" s="31">
         <f>'Financial Model'!B6</f>
         <v>1491164</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>'Financial Model'!C6</f>
         <v>1778131</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <f>'Financial Model'!D6</f>
         <v>2002741</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <f>'Financial Model'!E6</f>
         <v>2219491</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <f>'Financial Model'!F6</f>
         <v>2465218</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24" s="42">
+      <c r="A24" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="43">
         <f>'Financial Model'!B7</f>
         <v>-26164</v>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="44">
         <f>'Financial Model'!C7</f>
         <v>550669</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="44">
         <f>'Financial Model'!D7</f>
         <v>1449559</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="44">
         <f>'Financial Model'!E7</f>
         <v>2403509</v>
       </c>
-      <c r="F24" s="43">
+      <c r="F24" s="44">
         <f>'Financial Model'!F7</f>
         <v>3426282</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" s="30">
         <f>'Financial Model'!B8</f>
         <v>-26164</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>'Financial Model'!C8</f>
         <v>524505</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <f>'Financial Model'!D8</f>
         <v>1974064</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <f>'Financial Model'!E8</f>
         <v>4377573</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <f>'Financial Model'!F8</f>
         <v>7803855</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="44" t="str">
+      <c r="B26" s="45" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
@@ -3335,7 +3359,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3344,85 +3368,85 @@
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B29" s="29">
+      <c r="A29" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
         <v>12208.333333333334</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
         <v>11644</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
         <v>11507.666666666666</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
         <v>11557.5</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
         <v>11783</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="B30" s="41">
+      <c r="A30" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="42">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.5327883959044368</v>
       </c>
-      <c r="C30" s="41">
+      <c r="C30" s="42">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.4021994160082446</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="42">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.2713095617414477</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="42">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.20260480207657366</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="42">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.15898192310956463</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="B31" s="41">
+      <c r="A31" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" s="42">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.41228668941979524</v>
       </c>
-      <c r="C31" s="41">
+      <c r="C31" s="42">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.3327293026451391</v>
       </c>
-      <c r="D31" s="41">
+      <c r="D31" s="42">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.2880601338238276</v>
       </c>
-      <c r="E31" s="41">
+      <c r="E31" s="42">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.26524334847501624</v>
       </c>
-      <c r="F31" s="41">
+      <c r="F31" s="42">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.24984248493592465</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="B32" s="45">
+      <c r="A32" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" s="46">
         <f>IF(B20=0,0,B24/B20)</f>
         <v>-0.01785938566552901</v>
       </c>
@@ -3445,7 +3469,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3454,62 +3478,62 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="B35" s="41">
+      <c r="A35" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B35" s="42">
         <v>0.032764505119453925</v>
       </c>
-      <c r="C35" s="41">
+      <c r="C35" s="42">
         <v>0.03538302988663689</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="42">
         <v>0.03684500188280277</v>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="42">
         <v>0.03781094527363184</v>
       </c>
-      <c r="F35" s="41">
+      <c r="F35" s="42">
         <v>0.03819061359585844</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="B36" s="41">
+      <c r="A36" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="42">
         <v>0.8477815699658703</v>
       </c>
-      <c r="C36" s="41">
+      <c r="C36" s="42">
         <v>0.9066472002748196</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="42">
         <v>0.9356371114908901</v>
       </c>
-      <c r="E36" s="41">
+      <c r="E36" s="42">
         <v>0.9502920181700195</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="42">
         <v>0.9507765424764492</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B37" s="41">
+      <c r="A37" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="42">
         <v>0.11945392491467577</v>
       </c>
-      <c r="C37" s="41">
+      <c r="C37" s="42">
         <v>0.057969769838543454</v>
       </c>
-      <c r="D37" s="41">
+      <c r="D37" s="42">
         <v>0.0275178866263071</v>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="42">
         <v>0.01189703655634869</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="42">
         <v>0.011032843927692439</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -12,6 +12,7 @@
     <sheet sheetId="5" name="Capital &amp; Debt" state="visible" r:id="rId9"/>
     <sheet sheetId="6" name="Financial Model" state="visible" r:id="rId10"/>
     <sheet sheetId="7" name="Summary" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Financial Health" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
@@ -28,13 +29,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="218">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -517,21 +520,193 @@
   </si>
   <si>
     <t>Philanthropy %</t>
+  </si>
+  <si>
+    <t>Heritage Academy Charter — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Debt Service</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>0 months</t>
+  </si>
+  <si>
+    <t>60+ months</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 16% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 7% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 74.69x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>38.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>6 Healthy  |  0 Watch  |  1 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0;#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -652,6 +827,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -765,7 +946,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -815,11 +996,235 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="20" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="20" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3727,4 +4132,677 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:H35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="51" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="52">
+        <v>120</v>
+      </c>
+      <c r="D7" s="52">
+        <v>200</v>
+      </c>
+      <c r="E7" s="52">
+        <v>300</v>
+      </c>
+      <c r="F7" s="52">
+        <v>400</v>
+      </c>
+      <c r="G7" s="52">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="53">
+        <v>1465000</v>
+      </c>
+      <c r="D8" s="53">
+        <v>2328800</v>
+      </c>
+      <c r="E8" s="53">
+        <v>3452300</v>
+      </c>
+      <c r="F8" s="53">
+        <v>4623000</v>
+      </c>
+      <c r="G8" s="53">
+        <v>5891500</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C9" s="53">
+        <v>780535</v>
+      </c>
+      <c r="D9" s="53">
+        <v>936642</v>
+      </c>
+      <c r="E9" s="53">
+        <v>936642</v>
+      </c>
+      <c r="F9" s="53">
+        <v>936642</v>
+      </c>
+      <c r="G9" s="53">
+        <v>936642</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="53">
+        <v>604000</v>
+      </c>
+      <c r="D10" s="53">
+        <v>774860</v>
+      </c>
+      <c r="E10" s="53">
+        <v>994470</v>
+      </c>
+      <c r="F10" s="53">
+        <v>1226220</v>
+      </c>
+      <c r="G10" s="53">
+        <v>1471947</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="53">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="D11" s="53">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="E11" s="53">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="F11" s="53">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="G11" s="53">
+        <v>46628.6108154935</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="54" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="55">
+        <v>-26164</v>
+      </c>
+      <c r="D12" s="56">
+        <v>550669</v>
+      </c>
+      <c r="E12" s="56">
+        <v>1449559</v>
+      </c>
+      <c r="F12" s="56">
+        <v>2403509</v>
+      </c>
+      <c r="G12" s="56">
+        <v>3426282</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="54" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="55">
+        <v>-26164</v>
+      </c>
+      <c r="D13" s="56">
+        <v>524505</v>
+      </c>
+      <c r="E13" s="56">
+        <v>1974064</v>
+      </c>
+      <c r="F13" s="56">
+        <v>4377573</v>
+      </c>
+      <c r="G13" s="56">
+        <v>7803855</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" s="57">
+        <v>-0.01785938566552901</v>
+      </c>
+      <c r="D14" s="58">
+        <v>0.23646040879422878</v>
+      </c>
+      <c r="E14" s="58">
+        <v>0.41988210758045363</v>
+      </c>
+      <c r="F14" s="58">
+        <v>0.5199024443002379</v>
+      </c>
+      <c r="G14" s="58">
+        <v>0.5815636085886446</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="54" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="59">
+        <v>12208.333333333334</v>
+      </c>
+      <c r="D15" s="59">
+        <v>11644</v>
+      </c>
+      <c r="E15" s="59">
+        <v>11507.666666666666</v>
+      </c>
+      <c r="F15" s="59">
+        <v>11557.5</v>
+      </c>
+      <c r="G15" s="59">
+        <v>11783</v>
+      </c>
+      <c r="H15" s="60" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="58">
+        <v>0.5327883959044368</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0.4021994160082446</v>
+      </c>
+      <c r="E16" s="58">
+        <v>0.2713095617414477</v>
+      </c>
+      <c r="F16" s="58">
+        <v>0.20260480207657366</v>
+      </c>
+      <c r="G16" s="58">
+        <v>0.15898192310956463</v>
+      </c>
+      <c r="H16" s="60" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="58">
+        <v>0.12368600682593857</v>
+      </c>
+      <c r="D17" s="58">
+        <v>0.09981879079354174</v>
+      </c>
+      <c r="E17" s="58">
+        <v>0.08641804014714828</v>
+      </c>
+      <c r="F17" s="58">
+        <v>0.07957300454250486</v>
+      </c>
+      <c r="G17" s="58">
+        <v>0.07495274548077739</v>
+      </c>
+      <c r="H17" s="60" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="54" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="61">
+        <v>0.05492491467576792</v>
+      </c>
+      <c r="D18" s="58">
+        <v>0.2650712813466163</v>
+      </c>
+      <c r="E18" s="58">
+        <v>0.4406303044347247</v>
+      </c>
+      <c r="F18" s="58">
+        <v>0.5321518494484101</v>
+      </c>
+      <c r="G18" s="58">
+        <v>0.5911755919545107</v>
+      </c>
+      <c r="H18" s="60" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="62">
+        <v>3</v>
+      </c>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="60" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="63">
+        <v>1.7256572433263127</v>
+      </c>
+      <c r="D20" s="63">
+        <v>13.238610140941356</v>
+      </c>
+      <c r="E20" s="63">
+        <v>32.62348959996355</v>
+      </c>
+      <c r="F20" s="63">
+        <v>52.76026793366443</v>
+      </c>
+      <c r="G20" s="63">
+        <v>74.69471938123272</v>
+      </c>
+      <c r="H20" s="60" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="60" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="65" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="60" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="66" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="68" t="s">
+        <v>195</v>
+      </c>
+      <c r="E25" s="68"/>
+      <c r="F25" s="69" t="s">
+        <v>196</v>
+      </c>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="70" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="68" t="s">
+        <v>199</v>
+      </c>
+      <c r="E26" s="68"/>
+      <c r="F26" s="69" t="s">
+        <v>200</v>
+      </c>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="66" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D27" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" s="68"/>
+      <c r="F27" s="69" t="s">
+        <v>203</v>
+      </c>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="66" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="E28" s="68"/>
+      <c r="F28" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D29" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="E29" s="68"/>
+      <c r="F29" s="69" t="s">
+        <v>209</v>
+      </c>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="66" t="s">
+        <v>210</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D30" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="E30" s="68"/>
+      <c r="F30" s="69" t="s">
+        <v>212</v>
+      </c>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="66" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D31" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="E31" s="68"/>
+      <c r="F31" s="69" t="s">
+        <v>215</v>
+      </c>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C14&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C14&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C14&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&gt;=10000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&gt;=7000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&lt;7000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BHeritage Academy Charter&amp;R&amp;8&amp;IFinancial Health</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="220">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -475,6 +475,12 @@
   </si>
   <si>
     <t>Cumulative Net Income</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>Financial Model Summary</t>
@@ -946,7 +952,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -989,6 +995,12 @@
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1036,9 +1048,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3150,7 +3159,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3375,6 +3384,26 @@
       <c r="F9" s="39">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>37.98700966811049</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3400,18 +3429,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="A1" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
-        <v>147</v>
+      <c r="A2" s="43" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3485,12 +3514,12 @@
         <v>40</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3545,24 +3574,24 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C17" s="42">
+        <v>153</v>
+      </c>
+      <c r="C17" s="44">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="44">
         <f>IF(C16=0,0,(D16-C16)/C16)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="44">
         <f>IF(D16=0,0,(E16-D16)/D16)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="44">
         <f>IF(E16=0,0,(F16-E16)/E16)</f>
         <v>0.25</v>
       </c>
@@ -3691,23 +3720,23 @@
       <c r="A24" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="B24" s="43">
+      <c r="B24" s="45">
         <f>'Financial Model'!B7</f>
         <v>-26164</v>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="46">
         <f>'Financial Model'!C7</f>
         <v>550669</v>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="46">
         <f>'Financial Model'!D7</f>
         <v>1449559</v>
       </c>
-      <c r="E24" s="44">
+      <c r="E24" s="46">
         <f>'Financial Model'!E7</f>
         <v>2403509</v>
       </c>
-      <c r="F24" s="44">
+      <c r="F24" s="46">
         <f>'Financial Model'!F7</f>
         <v>3426282</v>
       </c>
@@ -3741,7 +3770,7 @@
       <c r="A26" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="45" t="str">
+      <c r="B26" s="47" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
@@ -3764,7 +3793,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -3774,7 +3803,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B29" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
@@ -3799,59 +3828,59 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="B30" s="42">
+        <v>156</v>
+      </c>
+      <c r="B30" s="44">
         <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
         <v>0.5327883959044368</v>
       </c>
-      <c r="C30" s="42">
+      <c r="C30" s="44">
         <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
         <v>0.4021994160082446</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="44">
         <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
         <v>0.2713095617414477</v>
       </c>
-      <c r="E30" s="42">
+      <c r="E30" s="44">
         <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
         <v>0.20260480207657366</v>
       </c>
-      <c r="F30" s="42">
+      <c r="F30" s="44">
         <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
         <v>0.15898192310956463</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B31" s="42">
+        <v>157</v>
+      </c>
+      <c r="B31" s="44">
         <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
         <v>0.41228668941979524</v>
       </c>
-      <c r="C31" s="42">
+      <c r="C31" s="44">
         <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
         <v>0.3327293026451391</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="44">
         <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
         <v>0.2880601338238276</v>
       </c>
-      <c r="E31" s="42">
+      <c r="E31" s="44">
         <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
         <v>0.26524334847501624</v>
       </c>
-      <c r="F31" s="42">
+      <c r="F31" s="44">
         <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
         <v>0.24984248493592465</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="B32" s="46">
+        <v>158</v>
+      </c>
+      <c r="B32" s="48">
         <f>IF(B20=0,0,B24/B20)</f>
         <v>-0.01785938566552901</v>
       </c>
@@ -3874,7 +3903,7 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -3884,61 +3913,61 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B35" s="42">
+        <v>160</v>
+      </c>
+      <c r="B35" s="44">
         <v>0.032764505119453925</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="44">
         <v>0.03538302988663689</v>
       </c>
-      <c r="D35" s="42">
+      <c r="D35" s="44">
         <v>0.03684500188280277</v>
       </c>
-      <c r="E35" s="42">
+      <c r="E35" s="44">
         <v>0.03781094527363184</v>
       </c>
-      <c r="F35" s="42">
+      <c r="F35" s="44">
         <v>0.03819061359585844</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="B36" s="42">
+        <v>161</v>
+      </c>
+      <c r="B36" s="44">
         <v>0.8477815699658703</v>
       </c>
-      <c r="C36" s="42">
+      <c r="C36" s="44">
         <v>0.9066472002748196</v>
       </c>
-      <c r="D36" s="42">
+      <c r="D36" s="44">
         <v>0.9356371114908901</v>
       </c>
-      <c r="E36" s="42">
+      <c r="E36" s="44">
         <v>0.9502920181700195</v>
       </c>
-      <c r="F36" s="42">
+      <c r="F36" s="44">
         <v>0.9507765424764492</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="B37" s="42">
+        <v>162</v>
+      </c>
+      <c r="B37" s="44">
         <v>0.11945392491467577</v>
       </c>
-      <c r="C37" s="42">
+      <c r="C37" s="44">
         <v>0.057969769838543454</v>
       </c>
-      <c r="D37" s="42">
+      <c r="D37" s="44">
         <v>0.0275178866263071</v>
       </c>
-      <c r="E37" s="42">
+      <c r="E37" s="44">
         <v>0.01189703655634869</v>
       </c>
-      <c r="F37" s="42">
+      <c r="F37" s="44">
         <v>0.011032843927692439</v>
       </c>
     </row>
@@ -4151,118 +4180,118 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="B2" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="47" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="B3" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="48" t="s">
-        <v>163</v>
-      </c>
-      <c r="D4" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="50" t="s">
+      <c r="B4" s="50" t="s">
         <v>165</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="51" t="s">
-        <v>167</v>
+      <c r="H6" s="53" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="52">
+        <v>170</v>
+      </c>
+      <c r="C7" s="54">
         <v>120</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="54">
         <v>200</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="54">
         <v>300</v>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="54">
         <v>400</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="54">
         <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="53">
+        <v>171</v>
+      </c>
+      <c r="C8" s="55">
         <v>1465000</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="55">
         <v>2328800</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="55">
         <v>3452300</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="55">
         <v>4623000</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="55">
         <v>5891500</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="53">
+        <v>172</v>
+      </c>
+      <c r="C9" s="55">
         <v>780535</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="55">
         <v>936642</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="55">
         <v>936642</v>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="55">
         <v>936642</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="55">
         <v>936642</v>
       </c>
     </row>
@@ -4270,419 +4299,419 @@
       <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="55">
         <v>604000</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="55">
         <v>774860</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="55">
         <v>994470</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="55">
         <v>1226220</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="55">
         <v>1471947</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C11" s="53">
+        <v>173</v>
+      </c>
+      <c r="C11" s="55">
         <v>46628.6108154935</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="55">
         <v>46628.6108154935</v>
       </c>
-      <c r="E11" s="53">
+      <c r="E11" s="55">
         <v>46628.6108154935</v>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="55">
         <v>46628.6108154935</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="55">
         <v>46628.6108154935</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="55">
+      <c r="C12" s="57">
         <v>-26164</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="58">
         <v>550669</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="58">
         <v>1449559</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="58">
         <v>2403509</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="58">
         <v>3426282</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="54" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" s="55">
+      <c r="B13" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="57">
         <v>-26164</v>
       </c>
-      <c r="D13" s="56">
+      <c r="D13" s="58">
         <v>524505</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="58">
         <v>1974064</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="58">
         <v>4377573</v>
       </c>
-      <c r="G13" s="56">
+      <c r="G13" s="58">
         <v>7803855</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="54" t="s">
-        <v>173</v>
-      </c>
-      <c r="C14" s="57">
+      <c r="B14" s="56" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="59">
         <v>-0.01785938566552901</v>
       </c>
-      <c r="D14" s="58">
+      <c r="D14" s="60">
         <v>0.23646040879422878</v>
       </c>
-      <c r="E14" s="58">
+      <c r="E14" s="60">
         <v>0.41988210758045363</v>
       </c>
-      <c r="F14" s="58">
+      <c r="F14" s="60">
         <v>0.5199024443002379</v>
       </c>
-      <c r="G14" s="58">
+      <c r="G14" s="60">
         <v>0.5815636085886446</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="54" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" s="59">
+      <c r="B15" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="61">
         <v>12208.333333333334</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="61">
         <v>11644</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="61">
         <v>11507.666666666666</v>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="61">
         <v>11557.5</v>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="61">
         <v>11783</v>
       </c>
-      <c r="H15" s="60" t="s">
-        <v>174</v>
+      <c r="H15" s="62" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="54" t="s">
-        <v>175</v>
-      </c>
-      <c r="C16" s="58">
+      <c r="B16" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="60">
         <v>0.5327883959044368</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D16" s="60">
         <v>0.4021994160082446</v>
       </c>
-      <c r="E16" s="58">
+      <c r="E16" s="60">
         <v>0.2713095617414477</v>
       </c>
-      <c r="F16" s="58">
+      <c r="F16" s="60">
         <v>0.20260480207657366</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G16" s="60">
         <v>0.15898192310956463</v>
       </c>
-      <c r="H16" s="60" t="s">
-        <v>176</v>
+      <c r="H16" s="62" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="54" t="s">
-        <v>177</v>
-      </c>
-      <c r="C17" s="58">
+      <c r="B17" s="56" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="60">
         <v>0.12368600682593857</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D17" s="60">
         <v>0.09981879079354174</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E17" s="60">
         <v>0.08641804014714828</v>
       </c>
-      <c r="F17" s="58">
+      <c r="F17" s="60">
         <v>0.07957300454250486</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G17" s="60">
         <v>0.07495274548077739</v>
       </c>
-      <c r="H17" s="60" t="s">
-        <v>178</v>
+      <c r="H17" s="62" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="54" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="61">
+      <c r="B18" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="63">
         <v>0.05492491467576792</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="60">
         <v>0.2650712813466163</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="60">
         <v>0.4406303044347247</v>
       </c>
-      <c r="F18" s="58">
+      <c r="F18" s="60">
         <v>0.5321518494484101</v>
       </c>
-      <c r="G18" s="58">
+      <c r="G18" s="60">
         <v>0.5911755919545107</v>
       </c>
-      <c r="H18" s="60" t="s">
-        <v>180</v>
+      <c r="H18" s="62" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="54" t="s">
-        <v>181</v>
-      </c>
-      <c r="C19" s="62">
+      <c r="B19" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="64">
         <v>3</v>
       </c>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="60" t="s">
-        <v>182</v>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="62" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="54" t="s">
-        <v>183</v>
-      </c>
-      <c r="C20" s="63">
+      <c r="B20" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" s="65">
         <v>1.7256572433263127</v>
       </c>
-      <c r="D20" s="63">
+      <c r="D20" s="65">
         <v>13.238610140941356</v>
       </c>
-      <c r="E20" s="63">
+      <c r="E20" s="65">
         <v>32.62348959996355</v>
       </c>
-      <c r="F20" s="63">
+      <c r="F20" s="65">
         <v>52.76026793366443</v>
       </c>
-      <c r="G20" s="63">
+      <c r="G20" s="65">
         <v>74.69471938123272</v>
       </c>
-      <c r="H20" s="60" t="s">
-        <v>184</v>
+      <c r="H20" s="62" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="54" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" s="64" t="s">
+      <c r="B21" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="60" t="s">
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="62" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="54" t="s">
-        <v>186</v>
-      </c>
-      <c r="C22" s="65" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="60" t="s">
+      <c r="B22" s="56" t="s">
         <v>188</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="62" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="C25" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D25" s="68" t="s">
+      <c r="B25" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="E25" s="68"/>
-      <c r="F25" s="69" t="s">
+      <c r="C25" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
+      <c r="D25" s="69" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="69"/>
+      <c r="F25" s="70" t="s">
+        <v>198</v>
+      </c>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="66" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="70" t="s">
-        <v>198</v>
-      </c>
-      <c r="D26" s="68" t="s">
+      <c r="B26" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="E26" s="68"/>
-      <c r="F26" s="69" t="s">
+      <c r="C26" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
+      <c r="D26" s="69" t="s">
+        <v>201</v>
+      </c>
+      <c r="E26" s="69"/>
+      <c r="F26" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="66" t="s">
-        <v>201</v>
-      </c>
-      <c r="C27" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D27" s="68" t="s">
-        <v>202</v>
-      </c>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69" t="s">
+      <c r="B27" s="68" t="s">
         <v>203</v>
       </c>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
+      <c r="C27" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="D27" s="69" t="s">
+        <v>204</v>
+      </c>
+      <c r="E27" s="69"/>
+      <c r="F27" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="66" t="s">
-        <v>204</v>
-      </c>
-      <c r="C28" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" s="68" t="s">
-        <v>205</v>
-      </c>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69" t="s">
+      <c r="B28" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
+      <c r="C28" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="69" t="s">
+        <v>207</v>
+      </c>
+      <c r="E28" s="69"/>
+      <c r="F28" s="70" t="s">
+        <v>208</v>
+      </c>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="66" t="s">
-        <v>207</v>
-      </c>
-      <c r="C29" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" s="68" t="s">
-        <v>208</v>
-      </c>
-      <c r="E29" s="68"/>
-      <c r="F29" s="69" t="s">
+      <c r="B29" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
+      <c r="C29" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70" t="s">
+        <v>211</v>
+      </c>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="66" t="s">
-        <v>210</v>
-      </c>
-      <c r="C30" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D30" s="68" t="s">
-        <v>211</v>
-      </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69" t="s">
+      <c r="B30" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
+      <c r="C30" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="69" t="s">
+        <v>213</v>
+      </c>
+      <c r="E30" s="69"/>
+      <c r="F30" s="70" t="s">
+        <v>214</v>
+      </c>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="66" t="s">
-        <v>213</v>
-      </c>
-      <c r="C31" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D31" s="68" t="s">
-        <v>214</v>
-      </c>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69" t="s">
+      <c r="B31" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
+      <c r="C31" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" s="69" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="69"/>
+      <c r="F31" s="70" t="s">
+        <v>217</v>
+      </c>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="66" t="s">
+      <c r="B33" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="54" t="s">
-        <v>216</v>
-      </c>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
+      <c r="C33" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="71" t="s">
-        <v>217</v>
-      </c>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
+      <c r="B35" s="72" t="s">
+        <v>219</v>
+      </c>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -4821,10 +4821,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="220">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -1045,7 +1045,9 @@
     <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4529,13 +4531,26 @@
       <c r="B21" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
+      <c r="C21" s="66" t="str">
+        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="41" t="str">
+        <f>IF('Financial Model'!C8&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="66" t="str">
+        <f>IF('Financial Model'!D8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="66" t="str">
+        <f>IF('Financial Model'!E8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="66" t="str">
+        <f>IF('Financial Model'!F8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="62" t="s">
         <v>66</v>
       </c>
@@ -4714,11 +4729,10 @@
       <c r="H35" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -4799,10 +4813,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="219">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -603,13 +603,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>0 months</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -952,7 +949,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1041,14 +1038,21 @@
     <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="170" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4496,10 +4500,18 @@
       <c r="C19" s="64">
         <v>3</v>
       </c>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
+      <c r="D19" s="64">
+        <v>3</v>
+      </c>
+      <c r="E19" s="64">
+        <v>3</v>
+      </c>
+      <c r="F19" s="64">
+        <v>3</v>
+      </c>
+      <c r="G19" s="64">
+        <v>3</v>
+      </c>
       <c r="H19" s="62" t="s">
         <v>184</v>
       </c>
@@ -4536,19 +4548,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="41" t="str">
-        <f>IF('Financial Model'!C8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="E21" s="66" t="str">
-        <f>IF('Financial Model'!D8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="66" t="str">
-        <f>IF('Financial Model'!E8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="66" t="str">
-        <f>IF('Financial Model'!F8&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="62" t="s">
@@ -4559,181 +4571,187 @@
       <c r="B22" s="56" t="s">
         <v>188</v>
       </c>
-      <c r="C22" s="67" t="s">
+      <c r="C22" s="67">
+        <v>0</v>
+      </c>
+      <c r="D22" s="67">
+        <v>4</v>
+      </c>
+      <c r="E22" s="68">
+        <v>12</v>
+      </c>
+      <c r="F22" s="64">
+        <v>24</v>
+      </c>
+      <c r="G22" s="64">
+        <v>38</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>189</v>
-      </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="62" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>192</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>193</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="69" t="s">
+        <v>194</v>
+      </c>
+      <c r="C25" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="D25" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="E25" s="70"/>
+      <c r="F25" s="71" t="s">
         <v>197</v>
       </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="70" t="s">
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="69" t="s">
         <v>198</v>
       </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="68" t="s">
+      <c r="C26" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="C26" s="71" t="s">
+      <c r="D26" s="70" t="s">
         <v>200</v>
       </c>
-      <c r="D26" s="69" t="s">
+      <c r="E26" s="70"/>
+      <c r="F26" s="71" t="s">
         <v>201</v>
       </c>
-      <c r="E26" s="69"/>
-      <c r="F26" s="70" t="s">
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="69" t="s">
         <v>202</v>
       </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="68" t="s">
+      <c r="C27" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27" s="70" t="s">
         <v>203</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="D27" s="69" t="s">
+      <c r="E27" s="70"/>
+      <c r="F27" s="71" t="s">
         <v>204</v>
       </c>
-      <c r="E27" s="69"/>
-      <c r="F27" s="70" t="s">
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="69" t="s">
         <v>205</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="68" t="s">
+      <c r="C28" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D28" s="70" t="s">
         <v>206</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="D28" s="69" t="s">
+      <c r="E28" s="70"/>
+      <c r="F28" s="71" t="s">
         <v>207</v>
       </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="70" t="s">
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="69" t="s">
         <v>208</v>
       </c>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="68" t="s">
+      <c r="C29" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D29" s="70" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="D29" s="69" t="s">
+      <c r="E29" s="70"/>
+      <c r="F29" s="71" t="s">
         <v>210</v>
       </c>
-      <c r="E29" s="69"/>
-      <c r="F29" s="70" t="s">
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="69" t="s">
         <v>211</v>
       </c>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="68" t="s">
+      <c r="C30" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="70" t="s">
         <v>212</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="D30" s="69" t="s">
+      <c r="E30" s="70"/>
+      <c r="F30" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="E30" s="69"/>
-      <c r="F30" s="70" t="s">
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="68" t="s">
+      <c r="C31" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="70" t="s">
         <v>215</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="D31" s="69" t="s">
+      <c r="E31" s="70"/>
+      <c r="F31" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="E31" s="69"/>
-      <c r="F31" s="70" t="s">
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="56" t="s">
         <v>217</v>
-      </c>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="68" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="56" t="s">
-        <v>218</v>
       </c>
       <c r="D33" s="56"/>
       <c r="E33" s="56"/>
       <c r="F33" s="56"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="72" t="s">
-        <v>219</v>
-      </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
+      <c r="B35" s="73" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -657,7 +657,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 7% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 6% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -4451,20 +4451,20 @@
       <c r="B17" s="56" t="s">
         <v>179</v>
       </c>
-      <c r="C17" s="60">
-        <v>0.12368600682593857</v>
+      <c r="C17" s="63">
+        <v>0.2197952218430034</v>
       </c>
       <c r="D17" s="60">
-        <v>0.09981879079354174</v>
+        <v>0.1424166952937135</v>
       </c>
       <c r="E17" s="60">
-        <v>0.08641804014714828</v>
+        <v>0.0989524664716276</v>
       </c>
       <c r="F17" s="60">
-        <v>0.07957300454250486</v>
+        <v>0.07610986978152713</v>
       </c>
       <c r="G17" s="60">
-        <v>0.07495274548077739</v>
+        <v>0.06151562859034203</v>
       </c>
       <c r="H17" s="62" t="s">
         <v>180</v>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -531,7 +531,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -2056,25 +2056,25 @@
       <c r="A11" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="31" t="str">
+      <c r="B11" s="31">
         <f>SUM(B9:B10)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="31" t="str">
+        <v>175000</v>
+      </c>
+      <c r="C11" s="31">
         <f>SUM(C9:C10)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="31" t="str">
+        <v>135000</v>
+      </c>
+      <c r="D11" s="31">
         <f>SUM(D9:D10)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="31" t="str">
+        <v>95000</v>
+      </c>
+      <c r="E11" s="31">
         <f>SUM(E9:E10)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="31" t="str">
+        <v>55000</v>
+      </c>
+      <c r="F11" s="31">
         <f>SUM(F9:F10)</f>
-        <v>0</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="221">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -607,6 +607,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -4175,7 +4181,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4590,170 +4596,191 @@
         <v>189</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="56" t="s">
         <v>190</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C23" s="67">
+        <v>0</v>
+      </c>
+      <c r="D23" s="64">
+        <v>109</v>
+      </c>
+      <c r="E23" s="64">
+        <v>364</v>
+      </c>
+      <c r="F23" s="64">
+        <v>723</v>
+      </c>
+      <c r="G23" s="64">
+        <v>1160</v>
+      </c>
+      <c r="H23" s="62" t="s">
         <v>191</v>
       </c>
-      <c r="D24" s="8" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
+      <c r="C25" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="69" t="s">
+      <c r="D25" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="E25" s="8"/>
+      <c r="F25" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D25" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71" t="s">
-        <v>197</v>
-      </c>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="69" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="70" t="s">
         <v>198</v>
-      </c>
-      <c r="C26" s="72" t="s">
-        <v>199</v>
-      </c>
-      <c r="D26" s="70" t="s">
-        <v>200</v>
       </c>
       <c r="E26" s="70"/>
       <c r="F26" s="71" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G26" s="71"/>
       <c r="H26" s="71"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="69" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="70" t="s">
         <v>202</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D27" s="70" t="s">
-        <v>203</v>
       </c>
       <c r="E27" s="70"/>
       <c r="F27" s="71" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G27" s="71"/>
       <c r="H27" s="71"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="69" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D28" s="70" t="s">
         <v>205</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D28" s="70" t="s">
-        <v>206</v>
       </c>
       <c r="E28" s="70"/>
       <c r="F28" s="71" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G28" s="71"/>
       <c r="H28" s="71"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="69" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" s="70" t="s">
         <v>208</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D29" s="70" t="s">
-        <v>209</v>
       </c>
       <c r="E29" s="70"/>
       <c r="F29" s="71" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G29" s="71"/>
       <c r="H29" s="71"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" s="70" t="s">
         <v>211</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="70" t="s">
-        <v>212</v>
       </c>
       <c r="E30" s="70"/>
       <c r="F30" s="71" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G30" s="71"/>
       <c r="H30" s="71"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="69" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" s="70" t="s">
         <v>214</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D31" s="70" t="s">
-        <v>215</v>
       </c>
       <c r="E31" s="70"/>
       <c r="F31" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G31" s="71"/>
       <c r="H31" s="71"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="69" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="69" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32" s="70" t="s">
+        <v>217</v>
+      </c>
+      <c r="E32" s="70"/>
+      <c r="F32" s="71" t="s">
+        <v>218</v>
+      </c>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="56" t="s">
-        <v>217</v>
-      </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="73" t="s">
-        <v>218</v>
-      </c>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
+      <c r="C34" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="73" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -4768,8 +4795,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="226">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -568,6 +568,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -955,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1041,6 +1056,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4181,7 +4208,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4430,365 +4457,440 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="C16" s="60">
-        <v>0.5327883959044368</v>
-      </c>
-      <c r="D16" s="60">
-        <v>0.4021994160082446</v>
-      </c>
-      <c r="E16" s="60">
-        <v>0.2713095617414477</v>
-      </c>
-      <c r="F16" s="60">
-        <v>0.20260480207657366</v>
-      </c>
-      <c r="G16" s="60">
-        <v>0.15898192310956463</v>
-      </c>
-      <c r="H16" s="62" t="s">
+      <c r="C16" s="63">
+        <v>11926.363423462444</v>
+      </c>
+      <c r="D16" s="63">
+        <v>8790.653054077467</v>
+      </c>
+      <c r="E16" s="63">
+        <v>6592.468702718311</v>
+      </c>
+      <c r="F16" s="63">
+        <v>5523.726527038733</v>
+      </c>
+      <c r="G16" s="63">
+        <v>4910.435221630987</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="56" t="s">
+      <c r="C17" s="55">
+        <v>650</v>
+      </c>
+      <c r="D17" s="55">
+        <v>670</v>
+      </c>
+      <c r="E17" s="55">
+        <v>690</v>
+      </c>
+      <c r="F17" s="55">
+        <v>710</v>
+      </c>
+      <c r="G17" s="55">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C17" s="63">
-        <v>0.2197952218430034</v>
-      </c>
-      <c r="D17" s="60">
-        <v>0.1424166952937135</v>
-      </c>
-      <c r="E17" s="60">
-        <v>0.0989524664716276</v>
-      </c>
-      <c r="F17" s="60">
-        <v>0.07610986978152713</v>
-      </c>
-      <c r="G17" s="60">
-        <v>0.06151562859034203</v>
-      </c>
-      <c r="H17" s="62" t="s">
+      <c r="C18" s="64">
+        <v>2683.3333333333335</v>
+      </c>
+      <c r="D18" s="61">
+        <v>1658.3</v>
+      </c>
+      <c r="E18" s="61">
+        <v>1138.712</v>
+      </c>
+      <c r="F18" s="61">
+        <v>879.6398199999999</v>
+      </c>
+      <c r="G18" s="61">
+        <v>724.8386516800001</v>
+      </c>
+      <c r="H18" s="62" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="56" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="56" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="63">
-        <v>0.05492491467576792</v>
-      </c>
-      <c r="D18" s="60">
-        <v>0.2650712813466163</v>
-      </c>
-      <c r="E18" s="60">
-        <v>0.4406303044347247</v>
-      </c>
-      <c r="F18" s="60">
-        <v>0.5321518494484101</v>
-      </c>
-      <c r="G18" s="60">
-        <v>0.5911755919545107</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="56" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="64">
-        <v>3</v>
-      </c>
-      <c r="D19" s="64">
-        <v>3</v>
-      </c>
-      <c r="E19" s="64">
-        <v>3</v>
-      </c>
-      <c r="F19" s="64">
-        <v>3</v>
-      </c>
-      <c r="G19" s="64">
-        <v>3</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>184</v>
+      <c r="C19" s="65">
+        <v>-218.03333333333333</v>
+      </c>
+      <c r="D19" s="66">
+        <v>2753.345</v>
+      </c>
+      <c r="E19" s="66">
+        <v>4831.863333333334</v>
+      </c>
+      <c r="F19" s="66">
+        <v>6008.7725</v>
+      </c>
+      <c r="G19" s="66">
+        <v>6852.564</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
-        <v>185</v>
-      </c>
-      <c r="C20" s="65">
-        <v>1.7256572433263127</v>
-      </c>
-      <c r="D20" s="65">
-        <v>13.238610140941356</v>
-      </c>
-      <c r="E20" s="65">
-        <v>32.62348959996355</v>
-      </c>
-      <c r="F20" s="65">
-        <v>52.76026793366443</v>
-      </c>
-      <c r="G20" s="65">
-        <v>74.69471938123272</v>
+        <v>182</v>
+      </c>
+      <c r="C20" s="60">
+        <v>0.5327883959044368</v>
+      </c>
+      <c r="D20" s="60">
+        <v>0.4021994160082446</v>
+      </c>
+      <c r="E20" s="60">
+        <v>0.2713095617414477</v>
+      </c>
+      <c r="F20" s="60">
+        <v>0.20260480207657366</v>
+      </c>
+      <c r="G20" s="60">
+        <v>0.15898192310956463</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="67">
+        <v>0.2197952218430034</v>
+      </c>
+      <c r="D21" s="60">
+        <v>0.1424166952937135</v>
+      </c>
+      <c r="E21" s="60">
+        <v>0.0989524664716276</v>
+      </c>
+      <c r="F21" s="60">
+        <v>0.07610986978152713</v>
+      </c>
+      <c r="G21" s="60">
+        <v>0.06151562859034203</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="67">
+        <v>0.05492491467576792</v>
+      </c>
+      <c r="D22" s="60">
+        <v>0.2650712813466163</v>
+      </c>
+      <c r="E22" s="60">
+        <v>0.4406303044347247</v>
+      </c>
+      <c r="F22" s="60">
+        <v>0.5321518494484101</v>
+      </c>
+      <c r="G22" s="60">
+        <v>0.5911755919545107</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="66" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="68">
+        <v>3</v>
+      </c>
+      <c r="D23" s="68">
+        <v>3</v>
+      </c>
+      <c r="E23" s="68">
+        <v>3</v>
+      </c>
+      <c r="F23" s="68">
+        <v>3</v>
+      </c>
+      <c r="G23" s="68">
+        <v>3</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C24" s="69">
+        <v>1.7256572433263127</v>
+      </c>
+      <c r="D24" s="69">
+        <v>13.238610140941356</v>
+      </c>
+      <c r="E24" s="69">
+        <v>32.62348959996355</v>
+      </c>
+      <c r="F24" s="69">
+        <v>52.76026793366443</v>
+      </c>
+      <c r="G24" s="69">
+        <v>74.69471938123272</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C25" s="70" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="41" t="str">
+      <c r="D25" s="41" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="66" t="str">
+      <c r="E25" s="70" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="66" t="str">
+      <c r="F25" s="70" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="66" t="str">
+      <c r="G25" s="70" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="62" t="s">
+      <c r="H25" s="62" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="56" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="67">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="71">
         <v>0</v>
       </c>
-      <c r="D22" s="67">
+      <c r="D26" s="71">
         <v>4</v>
       </c>
-      <c r="E22" s="68">
+      <c r="E26" s="72">
         <v>12</v>
       </c>
-      <c r="F22" s="64">
+      <c r="F26" s="68">
         <v>24</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G26" s="68">
         <v>38</v>
       </c>
-      <c r="H22" s="62" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="56" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="67">
+      <c r="H26" s="62" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="56" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="71">
         <v>0</v>
       </c>
-      <c r="D23" s="64">
+      <c r="D27" s="68">
         <v>109</v>
       </c>
-      <c r="E23" s="64">
+      <c r="E27" s="68">
         <v>364</v>
       </c>
-      <c r="F23" s="64">
+      <c r="F27" s="68">
         <v>723</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G27" s="68">
         <v>1160</v>
       </c>
-      <c r="H23" s="62" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="69" t="s">
+      <c r="H27" s="62" t="s">
         <v>196</v>
       </c>
-      <c r="C26" s="41" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="70" t="s">
+      <c r="C29" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71" t="s">
+      <c r="D29" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="69" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C27" s="72" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="70" t="s">
+      <c r="C30" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="E27" s="70"/>
-      <c r="F27" s="71" t="s">
+      <c r="D30" s="74" t="s">
         <v>203</v>
       </c>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="69" t="s">
+      <c r="E30" s="74"/>
+      <c r="F30" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="D28" s="70" t="s">
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71" t="s">
+      <c r="C31" s="76" t="s">
         <v>206</v>
       </c>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="69" t="s">
+      <c r="D31" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" s="70" t="s">
+      <c r="E31" s="74"/>
+      <c r="F31" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71" t="s">
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="73" t="s">
         <v>209</v>
       </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="69" t="s">
+      <c r="C32" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D32" s="74" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="D30" s="70" t="s">
+      <c r="E32" s="74"/>
+      <c r="F32" s="75" t="s">
         <v>211</v>
       </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71" t="s">
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="73" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="69" t="s">
+      <c r="C33" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="74" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="D31" s="70" t="s">
+      <c r="E33" s="74"/>
+      <c r="F33" s="75" t="s">
         <v>214</v>
       </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="71" t="s">
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="73" t="s">
         <v>215</v>
       </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="69" t="s">
+      <c r="C34" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="74" t="s">
         <v>216</v>
       </c>
-      <c r="C32" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="D32" s="70" t="s">
+      <c r="E34" s="74"/>
+      <c r="F34" s="75" t="s">
         <v>217</v>
       </c>
-      <c r="E32" s="70"/>
-      <c r="F32" s="71" t="s">
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="73" t="s">
         <v>218</v>
       </c>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="69" t="s">
+      <c r="C35" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D35" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="E35" s="74"/>
+      <c r="F35" s="75" t="s">
+        <v>220</v>
+      </c>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="73" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="E36" s="74"/>
+      <c r="F36" s="75" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="73" t="s">
-        <v>220</v>
-      </c>
-      <c r="C36" s="73"/>
-      <c r="D36" s="73"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="73"/>
-      <c r="H36" s="73"/>
+      <c r="C38" s="56" t="s">
+        <v>224</v>
+      </c>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="77" t="s">
+        <v>225</v>
+      </c>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -4797,8 +4899,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4844,48 +4954,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="219">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -570,21 +570,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -622,12 +607,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>Days Cash on Hand</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -970,7 +949,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1056,18 +1035,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4208,7 +4175,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4457,458 +4424,352 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="C16" s="63">
-        <v>11926.363423462444</v>
-      </c>
-      <c r="D16" s="63">
-        <v>8790.653054077467</v>
-      </c>
-      <c r="E16" s="63">
-        <v>6592.468702718311</v>
-      </c>
-      <c r="F16" s="63">
-        <v>5523.726527038733</v>
-      </c>
-      <c r="G16" s="63">
-        <v>4910.435221630987</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="C16" s="60">
+        <v>0.5327883959044368</v>
+      </c>
+      <c r="D16" s="60">
+        <v>0.4021994160082446</v>
+      </c>
+      <c r="E16" s="60">
+        <v>0.2713095617414477</v>
+      </c>
+      <c r="F16" s="60">
+        <v>0.20260480207657366</v>
+      </c>
+      <c r="G16" s="60">
+        <v>0.15898192310956463</v>
+      </c>
+      <c r="H16" s="62" t="s">
         <v>178</v>
       </c>
-      <c r="C17" s="55">
-        <v>650</v>
-      </c>
-      <c r="D17" s="55">
-        <v>670</v>
-      </c>
-      <c r="E17" s="55">
-        <v>690</v>
-      </c>
-      <c r="F17" s="55">
-        <v>710</v>
-      </c>
-      <c r="G17" s="55">
-        <v>732</v>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="56" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="63">
+        <v>0.2197952218430034</v>
+      </c>
+      <c r="D17" s="60">
+        <v>0.1424166952937135</v>
+      </c>
+      <c r="E17" s="60">
+        <v>0.0989524664716276</v>
+      </c>
+      <c r="F17" s="60">
+        <v>0.07610986978152713</v>
+      </c>
+      <c r="G17" s="60">
+        <v>0.06151562859034203</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="64">
-        <v>2683.3333333333335</v>
-      </c>
-      <c r="D18" s="61">
-        <v>1658.3</v>
-      </c>
-      <c r="E18" s="61">
-        <v>1138.712</v>
-      </c>
-      <c r="F18" s="61">
-        <v>879.6398199999999</v>
-      </c>
-      <c r="G18" s="61">
-        <v>724.8386516800001</v>
+      <c r="B18" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="63">
+        <v>0.05492491467576792</v>
+      </c>
+      <c r="D18" s="60">
+        <v>0.2650712813466163</v>
+      </c>
+      <c r="E18" s="60">
+        <v>0.4406303044347247</v>
+      </c>
+      <c r="F18" s="60">
+        <v>0.5321518494484101</v>
+      </c>
+      <c r="G18" s="60">
+        <v>0.5911755919545107</v>
       </c>
       <c r="H18" s="62" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="C19" s="65">
-        <v>-218.03333333333333</v>
-      </c>
-      <c r="D19" s="66">
-        <v>2753.345</v>
-      </c>
-      <c r="E19" s="66">
-        <v>4831.863333333334</v>
-      </c>
-      <c r="F19" s="66">
-        <v>6008.7725</v>
-      </c>
-      <c r="G19" s="66">
-        <v>6852.564</v>
+        <v>183</v>
+      </c>
+      <c r="C19" s="64">
+        <v>3</v>
+      </c>
+      <c r="D19" s="64">
+        <v>3</v>
+      </c>
+      <c r="E19" s="64">
+        <v>3</v>
+      </c>
+      <c r="F19" s="64">
+        <v>3</v>
+      </c>
+      <c r="G19" s="64">
+        <v>3</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" s="60">
-        <v>0.5327883959044368</v>
-      </c>
-      <c r="D20" s="60">
-        <v>0.4021994160082446</v>
-      </c>
-      <c r="E20" s="60">
-        <v>0.2713095617414477</v>
-      </c>
-      <c r="F20" s="60">
-        <v>0.20260480207657366</v>
-      </c>
-      <c r="G20" s="60">
-        <v>0.15898192310956463</v>
+        <v>185</v>
+      </c>
+      <c r="C20" s="65">
+        <v>1.7256572433263127</v>
+      </c>
+      <c r="D20" s="65">
+        <v>13.238610140941356</v>
+      </c>
+      <c r="E20" s="65">
+        <v>32.62348959996355</v>
+      </c>
+      <c r="F20" s="65">
+        <v>52.76026793366443</v>
+      </c>
+      <c r="G20" s="65">
+        <v>74.69471938123272</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="67">
-        <v>0.2197952218430034</v>
-      </c>
-      <c r="D21" s="60">
-        <v>0.1424166952937135</v>
-      </c>
-      <c r="E21" s="60">
-        <v>0.0989524664716276</v>
-      </c>
-      <c r="F21" s="60">
-        <v>0.07610986978152713</v>
-      </c>
-      <c r="G21" s="60">
-        <v>0.06151562859034203</v>
+        <v>187</v>
+      </c>
+      <c r="C21" s="66" t="str">
+        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="41" t="str">
+        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="66" t="str">
+        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="66" t="str">
+        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="66" t="str">
+        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="56" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C22" s="67">
-        <v>0.05492491467576792</v>
-      </c>
-      <c r="D22" s="60">
-        <v>0.2650712813466163</v>
-      </c>
-      <c r="E22" s="60">
-        <v>0.4406303044347247</v>
-      </c>
-      <c r="F22" s="60">
-        <v>0.5321518494484101</v>
-      </c>
-      <c r="G22" s="60">
-        <v>0.5911755919545107</v>
+        <v>0</v>
+      </c>
+      <c r="D22" s="67">
+        <v>4</v>
+      </c>
+      <c r="E22" s="68">
+        <v>12</v>
+      </c>
+      <c r="F22" s="64">
+        <v>24</v>
+      </c>
+      <c r="G22" s="64">
+        <v>38</v>
       </c>
       <c r="H22" s="62" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="56" t="s">
-        <v>188</v>
-      </c>
-      <c r="C23" s="68">
-        <v>3</v>
-      </c>
-      <c r="D23" s="68">
-        <v>3</v>
-      </c>
-      <c r="E23" s="68">
-        <v>3</v>
-      </c>
-      <c r="F23" s="68">
-        <v>3</v>
-      </c>
-      <c r="G23" s="68">
-        <v>3</v>
-      </c>
-      <c r="H23" s="62" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="56" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C24" s="69">
-        <v>1.7256572433263127</v>
-      </c>
-      <c r="D24" s="69">
-        <v>13.238610140941356</v>
-      </c>
-      <c r="E24" s="69">
-        <v>32.62348959996355</v>
-      </c>
-      <c r="F24" s="69">
-        <v>52.76026793366443</v>
-      </c>
-      <c r="G24" s="69">
-        <v>74.69471938123272</v>
-      </c>
-      <c r="H24" s="62" t="s">
+      <c r="C24" s="8" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="56" t="s">
+      <c r="D24" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C25" s="70" t="str">
-        <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="41" t="str">
-        <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="E25" s="70" t="str">
-        <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="70" t="str">
-        <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="70" t="str">
-        <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="56" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C26" s="71">
-        <v>0</v>
-      </c>
-      <c r="D26" s="71">
-        <v>4</v>
-      </c>
-      <c r="E26" s="72">
-        <v>12</v>
-      </c>
-      <c r="F26" s="68">
-        <v>24</v>
-      </c>
-      <c r="G26" s="68">
-        <v>38</v>
-      </c>
-      <c r="H26" s="62" t="s">
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="69" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="56" t="s">
+      <c r="C25" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="C27" s="71">
-        <v>0</v>
-      </c>
-      <c r="D27" s="68">
-        <v>109</v>
-      </c>
-      <c r="E27" s="68">
-        <v>364</v>
-      </c>
-      <c r="F27" s="68">
-        <v>723</v>
-      </c>
-      <c r="G27" s="68">
-        <v>1160</v>
-      </c>
-      <c r="H27" s="62" t="s">
+      <c r="D25" s="70" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="E25" s="70"/>
+      <c r="F25" s="71" t="s">
         <v>197</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="69" t="s">
         <v>198</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="C26" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
+      <c r="D26" s="70" t="s">
         <v>200</v>
       </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="71" t="s">
+        <v>201</v>
+      </c>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="69" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27" s="70" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" s="70"/>
+      <c r="F27" s="71" t="s">
+        <v>204</v>
+      </c>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="69" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D28" s="70" t="s">
+        <v>206</v>
+      </c>
+      <c r="E28" s="70"/>
+      <c r="F28" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D29" s="70" t="s">
+        <v>209</v>
+      </c>
+      <c r="E29" s="70"/>
+      <c r="F29" s="71" t="s">
+        <v>210</v>
+      </c>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="73" t="s">
-        <v>201</v>
+      <c r="B30" s="69" t="s">
+        <v>211</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D30" s="74" t="s">
-        <v>203</v>
-      </c>
-      <c r="E30" s="74"/>
-      <c r="F30" s="75" t="s">
-        <v>204</v>
-      </c>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
+        <v>195</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>212</v>
+      </c>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71" t="s">
+        <v>213</v>
+      </c>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="C31" s="76" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="74" t="s">
-        <v>207</v>
-      </c>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75" t="s">
-        <v>208</v>
-      </c>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="73" t="s">
-        <v>209</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D32" s="74" t="s">
-        <v>210</v>
-      </c>
-      <c r="E32" s="74"/>
-      <c r="F32" s="75" t="s">
-        <v>211</v>
-      </c>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="73" t="s">
-        <v>212</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D33" s="74" t="s">
-        <v>213</v>
-      </c>
-      <c r="E33" s="74"/>
-      <c r="F33" s="75" t="s">
+      <c r="B31" s="69" t="s">
         <v>214</v>
       </c>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="73" t="s">
+      <c r="C31" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="70" t="s">
         <v>215</v>
       </c>
-      <c r="C34" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D34" s="74" t="s">
+      <c r="E31" s="70"/>
+      <c r="F31" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="E34" s="74"/>
-      <c r="F34" s="75" t="s">
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="73" t="s">
         <v>218</v>
       </c>
-      <c r="C35" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D35" s="74" t="s">
-        <v>219</v>
-      </c>
-      <c r="E35" s="74"/>
-      <c r="F35" s="75" t="s">
-        <v>220</v>
-      </c>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="73" t="s">
-        <v>221</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="D36" s="74" t="s">
-        <v>222</v>
-      </c>
-      <c r="E36" s="74"/>
-      <c r="F36" s="75" t="s">
-        <v>223</v>
-      </c>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="73" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="56" t="s">
-        <v>224</v>
-      </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="77" t="s">
-        <v>225</v>
-      </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4954,48 +4815,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="226">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -570,6 +570,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -607,6 +622,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -949,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1035,6 +1056,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4175,7 +4208,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4424,352 +4457,458 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="C16" s="60">
-        <v>0.5327883959044368</v>
-      </c>
-      <c r="D16" s="60">
-        <v>0.4021994160082446</v>
-      </c>
-      <c r="E16" s="60">
-        <v>0.2713095617414477</v>
-      </c>
-      <c r="F16" s="60">
-        <v>0.20260480207657366</v>
-      </c>
-      <c r="G16" s="60">
-        <v>0.15898192310956463</v>
-      </c>
-      <c r="H16" s="62" t="s">
+      <c r="C16" s="63">
+        <v>11926.363423462444</v>
+      </c>
+      <c r="D16" s="63">
+        <v>8790.653054077467</v>
+      </c>
+      <c r="E16" s="63">
+        <v>6592.468702718311</v>
+      </c>
+      <c r="F16" s="63">
+        <v>5523.726527038733</v>
+      </c>
+      <c r="G16" s="63">
+        <v>4910.435221630987</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="56" t="s">
+      <c r="C17" s="55">
+        <v>650</v>
+      </c>
+      <c r="D17" s="55">
+        <v>670</v>
+      </c>
+      <c r="E17" s="55">
+        <v>690</v>
+      </c>
+      <c r="F17" s="55">
+        <v>710</v>
+      </c>
+      <c r="G17" s="55">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C17" s="63">
-        <v>0.2197952218430034</v>
-      </c>
-      <c r="D17" s="60">
-        <v>0.1424166952937135</v>
-      </c>
-      <c r="E17" s="60">
-        <v>0.0989524664716276</v>
-      </c>
-      <c r="F17" s="60">
-        <v>0.07610986978152713</v>
-      </c>
-      <c r="G17" s="60">
-        <v>0.06151562859034203</v>
-      </c>
-      <c r="H17" s="62" t="s">
+      <c r="C18" s="64">
+        <v>2683.3333333333335</v>
+      </c>
+      <c r="D18" s="61">
+        <v>1658.3</v>
+      </c>
+      <c r="E18" s="61">
+        <v>1138.712</v>
+      </c>
+      <c r="F18" s="61">
+        <v>879.6398199999999</v>
+      </c>
+      <c r="G18" s="61">
+        <v>724.8386516800001</v>
+      </c>
+      <c r="H18" s="62" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="56" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="56" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="63">
-        <v>0.05492491467576792</v>
-      </c>
-      <c r="D18" s="60">
-        <v>0.2650712813466163</v>
-      </c>
-      <c r="E18" s="60">
-        <v>0.4406303044347247</v>
-      </c>
-      <c r="F18" s="60">
-        <v>0.5321518494484101</v>
-      </c>
-      <c r="G18" s="60">
-        <v>0.5911755919545107</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="56" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="64">
-        <v>3</v>
-      </c>
-      <c r="D19" s="64">
-        <v>3</v>
-      </c>
-      <c r="E19" s="64">
-        <v>3</v>
-      </c>
-      <c r="F19" s="64">
-        <v>3</v>
-      </c>
-      <c r="G19" s="64">
-        <v>3</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>184</v>
+      <c r="C19" s="65">
+        <v>-218.03333333333333</v>
+      </c>
+      <c r="D19" s="66">
+        <v>2753.345</v>
+      </c>
+      <c r="E19" s="66">
+        <v>4831.863333333334</v>
+      </c>
+      <c r="F19" s="66">
+        <v>6008.7725</v>
+      </c>
+      <c r="G19" s="66">
+        <v>6852.564</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
-        <v>185</v>
-      </c>
-      <c r="C20" s="65">
-        <v>1.7256572433263127</v>
-      </c>
-      <c r="D20" s="65">
-        <v>13.238610140941356</v>
-      </c>
-      <c r="E20" s="65">
-        <v>32.62348959996355</v>
-      </c>
-      <c r="F20" s="65">
-        <v>52.76026793366443</v>
-      </c>
-      <c r="G20" s="65">
-        <v>74.69471938123272</v>
+        <v>182</v>
+      </c>
+      <c r="C20" s="60">
+        <v>0.5327883959044368</v>
+      </c>
+      <c r="D20" s="60">
+        <v>0.4021994160082446</v>
+      </c>
+      <c r="E20" s="60">
+        <v>0.2713095617414477</v>
+      </c>
+      <c r="F20" s="60">
+        <v>0.20260480207657366</v>
+      </c>
+      <c r="G20" s="60">
+        <v>0.15898192310956463</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="67">
+        <v>0.2197952218430034</v>
+      </c>
+      <c r="D21" s="60">
+        <v>0.1424166952937135</v>
+      </c>
+      <c r="E21" s="60">
+        <v>0.0989524664716276</v>
+      </c>
+      <c r="F21" s="60">
+        <v>0.07610986978152713</v>
+      </c>
+      <c r="G21" s="60">
+        <v>0.06151562859034203</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="67">
+        <v>0.05492491467576792</v>
+      </c>
+      <c r="D22" s="60">
+        <v>0.2650712813466163</v>
+      </c>
+      <c r="E22" s="60">
+        <v>0.4406303044347247</v>
+      </c>
+      <c r="F22" s="60">
+        <v>0.5321518494484101</v>
+      </c>
+      <c r="G22" s="60">
+        <v>0.5911755919545107</v>
+      </c>
+      <c r="H22" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="66" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="68">
+        <v>3</v>
+      </c>
+      <c r="D23" s="68">
+        <v>3</v>
+      </c>
+      <c r="E23" s="68">
+        <v>3</v>
+      </c>
+      <c r="F23" s="68">
+        <v>3</v>
+      </c>
+      <c r="G23" s="68">
+        <v>3</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C24" s="69">
+        <v>1.7256572433263127</v>
+      </c>
+      <c r="D24" s="69">
+        <v>13.238610140941356</v>
+      </c>
+      <c r="E24" s="69">
+        <v>32.62348959996355</v>
+      </c>
+      <c r="F24" s="69">
+        <v>52.76026793366443</v>
+      </c>
+      <c r="G24" s="69">
+        <v>74.69471938123272</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C25" s="70" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="41" t="str">
+      <c r="D25" s="41" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="66" t="str">
+      <c r="E25" s="70" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="66" t="str">
+      <c r="F25" s="70" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="66" t="str">
+      <c r="G25" s="70" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="62" t="s">
+      <c r="H25" s="62" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="56" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="67">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" s="71">
         <v>0</v>
       </c>
-      <c r="D22" s="67">
+      <c r="D26" s="71">
         <v>4</v>
       </c>
-      <c r="E22" s="68">
+      <c r="E26" s="72">
         <v>12</v>
       </c>
-      <c r="F22" s="64">
+      <c r="F26" s="68">
         <v>24</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G26" s="68">
         <v>38</v>
       </c>
-      <c r="H22" s="62" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="69" t="s">
+      <c r="H26" s="62" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="41" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="56" t="s">
         <v>195</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="C27" s="71">
+        <v>0</v>
+      </c>
+      <c r="D27" s="68">
+        <v>109</v>
+      </c>
+      <c r="E27" s="68">
+        <v>364</v>
+      </c>
+      <c r="F27" s="68">
+        <v>723</v>
+      </c>
+      <c r="G27" s="68">
+        <v>1160</v>
+      </c>
+      <c r="H27" s="62" t="s">
         <v>196</v>
       </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="69" t="s">
+      <c r="C29" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="D29" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="D26" s="70" t="s">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71" t="s">
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="73" t="s">
         <v>201</v>
       </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="69" t="s">
+      <c r="C30" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D27" s="70" t="s">
+      <c r="D30" s="74" t="s">
         <v>203</v>
       </c>
-      <c r="E27" s="70"/>
-      <c r="F27" s="71" t="s">
+      <c r="E30" s="74"/>
+      <c r="F30" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="69" t="s">
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="73" t="s">
         <v>205</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D28" s="70" t="s">
+      <c r="C31" s="76" t="s">
         <v>206</v>
       </c>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71" t="s">
+      <c r="D31" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="69" t="s">
+      <c r="E31" s="74"/>
+      <c r="F31" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D29" s="70" t="s">
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="73" t="s">
         <v>209</v>
       </c>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71" t="s">
+      <c r="C32" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D32" s="74" t="s">
         <v>210</v>
       </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="69" t="s">
+      <c r="E32" s="74"/>
+      <c r="F32" s="75" t="s">
         <v>211</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="70" t="s">
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="73" t="s">
         <v>212</v>
       </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71" t="s">
+      <c r="C33" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="74" t="s">
         <v>213</v>
       </c>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="69" t="s">
+      <c r="E33" s="74"/>
+      <c r="F33" s="75" t="s">
         <v>214</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D31" s="70" t="s">
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="73" t="s">
         <v>215</v>
       </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="71" t="s">
+      <c r="C34" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="74" t="s">
         <v>216</v>
       </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="56" t="s">
+      <c r="E34" s="74"/>
+      <c r="F34" s="75" t="s">
         <v>217</v>
       </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="73" t="s">
         <v>218</v>
       </c>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
+      <c r="C35" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D35" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="E35" s="74"/>
+      <c r="F35" s="75" t="s">
+        <v>220</v>
+      </c>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="73" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="E36" s="74"/>
+      <c r="F36" s="75" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="73" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>224</v>
+      </c>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="77" t="s">
+        <v>225</v>
+      </c>
+      <c r="C40" s="77"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4815,48 +4954,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -15,7 +15,7 @@
     <sheet sheetId="9" name="Financial Health" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$E33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Financial Health'!$1:$1</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="227">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -168,6 +168,9 @@
     <t>July</t>
   </si>
   <si>
+    <t>Accounting Basis</t>
+  </si>
+  <si>
     <t>Year 1 Operating Months</t>
   </si>
   <si>
@@ -531,7 +534,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -660,7 +663,7 @@
     <t>○ Needs attention</t>
   </si>
   <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+    <t>Cash goes negative in month 1. The school will need outside funding to continue operating.</t>
   </si>
   <si>
     <t>Secure a line of credit or bridge funding before operations begin.</t>
@@ -1610,7 +1613,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1727,70 +1730,70 @@
       <c r="A14" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="23">
-        <v>10</v>
+      <c r="B14" s="23" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>45</v>
+      <c r="B15" s="23">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>46</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>50</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="23" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="B20" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="8"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="24">
-        <v>120</v>
-      </c>
+      <c r="B22" s="8"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>56</v>
       </c>
       <c r="B23" s="24">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1798,7 +1801,7 @@
         <v>57</v>
       </c>
       <c r="B24" s="24">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1806,7 +1809,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="24">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1814,22 +1817,22 @@
         <v>59</v>
       </c>
       <c r="B26" s="24">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="24">
         <v>500</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="8"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="29" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="25">
-        <v>0</v>
-      </c>
+      <c r="B29" s="8"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
@@ -1843,16 +1846,24 @@
       <c r="A31" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="26">
-        <v>0.8333333333333334</v>
+      <c r="B31" s="25">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
         <v>65</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1885,49 +1896,49 @@
         <v>23</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="29">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>120</v>
       </c>
       <c r="C2" s="29">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>200</v>
       </c>
       <c r="D2" s="29">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>300</v>
       </c>
       <c r="E2" s="29">
-        <f>Assumptions!B25</f>
+        <f>Assumptions!B26</f>
         <v>400</v>
       </c>
       <c r="F2" s="29">
-        <f>Assumptions!B26</f>
+        <f>Assumptions!B27</f>
         <v>500</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1937,82 +1948,82 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B4" s="30">
-        <f>8500*Assumptions!B22</f>
+        <f>8500*Assumptions!B23</f>
         <v>1020000</v>
       </c>
       <c r="C4" s="30">
-        <f>8670*Assumptions!B23</f>
+        <f>8670*Assumptions!B24</f>
         <v>1734000</v>
       </c>
       <c r="D4" s="30">
-        <f>8843*Assumptions!B24</f>
+        <f>8843*Assumptions!B25</f>
         <v>2652900</v>
       </c>
       <c r="E4" s="30">
-        <f>9020*Assumptions!B25</f>
+        <f>9020*Assumptions!B26</f>
         <v>3608000</v>
       </c>
       <c r="F4" s="30">
-        <f>9200*Assumptions!B26</f>
+        <f>9200*Assumptions!B27</f>
         <v>4600000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="30">
-        <f>750*Assumptions!B22</f>
+        <f>750*Assumptions!B23</f>
         <v>90000</v>
       </c>
       <c r="C5" s="30">
-        <f>765*Assumptions!B23</f>
+        <f>765*Assumptions!B24</f>
         <v>153000</v>
       </c>
       <c r="D5" s="30">
-        <f>780*Assumptions!B24</f>
+        <f>780*Assumptions!B25</f>
         <v>234000</v>
       </c>
       <c r="E5" s="30">
-        <f>796*Assumptions!B25</f>
+        <f>796*Assumptions!B26</f>
         <v>318400</v>
       </c>
       <c r="F5" s="30">
-        <f>812*Assumptions!B26</f>
+        <f>812*Assumptions!B27</f>
         <v>406000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="30">
-        <f>1100*Assumptions!B22</f>
+        <f>1100*Assumptions!B23</f>
         <v>132000</v>
       </c>
       <c r="C6" s="30">
-        <f>1122*Assumptions!B23</f>
+        <f>1122*Assumptions!B24</f>
         <v>224400</v>
       </c>
       <c r="D6" s="30">
-        <f>1144*Assumptions!B24</f>
+        <f>1144*Assumptions!B25</f>
         <v>343200</v>
       </c>
       <c r="E6" s="30">
-        <f>1167*Assumptions!B25</f>
+        <f>1167*Assumptions!B26</f>
         <v>466800</v>
       </c>
       <c r="F6" s="30">
-        <f>1191*Assumptions!B26</f>
+        <f>1191*Assumptions!B27</f>
         <v>595500</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="31">
         <f>SUM(B4:B6)</f>
@@ -2037,7 +2048,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2047,7 +2058,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" s="30">
         <v>150000</v>
@@ -2067,7 +2078,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="30">
         <v>25000</v>
@@ -2087,7 +2098,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B9:B10)</f>
@@ -2112,7 +2123,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2122,32 +2133,32 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="30">
-        <f>400*Assumptions!B22</f>
+        <f>400*Assumptions!B23</f>
         <v>48000</v>
       </c>
       <c r="C13" s="30">
-        <f>412*Assumptions!B23</f>
+        <f>412*Assumptions!B24</f>
         <v>82400</v>
       </c>
       <c r="D13" s="30">
-        <f>424*Assumptions!B24</f>
+        <f>424*Assumptions!B25</f>
         <v>127200</v>
       </c>
       <c r="E13" s="30">
-        <f>437*Assumptions!B25</f>
+        <f>437*Assumptions!B26</f>
         <v>174800</v>
       </c>
       <c r="F13" s="30">
-        <f>450*Assumptions!B26</f>
+        <f>450*Assumptions!B27</f>
         <v>225000</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B13:B13)</f>
@@ -2172,7 +2183,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B16" s="31">
         <f>B7+B11+B14</f>
@@ -2219,7 +2230,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -2231,39 +2242,39 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4" s="26">
         <v>1</v>
@@ -2283,13 +2294,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>97</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>96</v>
       </c>
       <c r="D5" s="26">
         <v>1</v>
@@ -2309,13 +2320,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" s="26">
         <v>5</v>
@@ -2335,13 +2346,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>99</v>
-      </c>
       <c r="C7" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" s="26">
         <v>1</v>
@@ -2361,13 +2372,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" s="26">
         <v>3</v>
@@ -2387,13 +2398,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" s="26">
         <v>1</v>
@@ -2413,13 +2424,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="26">
         <v>2</v>
@@ -2439,7 +2450,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2451,7 +2462,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B13" s="34">
         <v>7</v>
@@ -2459,7 +2470,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B14" s="34">
         <v>14</v>
@@ -2467,7 +2478,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B15" s="35">
         <v>708000</v>
@@ -2475,7 +2486,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B16" s="35">
         <v>174480</v>
@@ -2483,7 +2494,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B17" s="35">
         <v>54162</v>
@@ -2491,7 +2502,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" s="35">
         <v>0</v>
@@ -2499,7 +2510,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B19" s="36">
         <v>936642</v>
@@ -2507,7 +2518,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2520,24 +2531,24 @@
         <v>23</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B23" s="30">
         <v>936642</v>
@@ -2557,35 +2568,35 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B24" s="37">
-        <f>(1+Assumptions!B29)^0</f>
+        <f>(1+Assumptions!B30)^0</f>
         <v>1</v>
       </c>
       <c r="C24" s="37">
-        <f>(1+Assumptions!B29)^1</f>
+        <f>(1+Assumptions!B30)^1</f>
         <v>1</v>
       </c>
       <c r="D24" s="37">
-        <f>(1+Assumptions!B29)^2</f>
+        <f>(1+Assumptions!B30)^2</f>
         <v>1</v>
       </c>
       <c r="E24" s="37">
-        <f>(1+Assumptions!B29)^3</f>
+        <f>(1+Assumptions!B30)^3</f>
         <v>1</v>
       </c>
       <c r="F24" s="37">
-        <f>(1+Assumptions!B29)^4</f>
+        <f>(1+Assumptions!B30)^4</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B25" s="38">
-        <f>Assumptions!B31</f>
+        <f>Assumptions!B32</f>
         <v>0.8333333333333334</v>
       </c>
       <c r="C25" s="38">
@@ -2603,7 +2614,7 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26" s="31">
         <f>B23*B24*B25</f>
@@ -2656,49 +2667,49 @@
         <v>23</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="29">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B23</f>
         <v>120</v>
       </c>
       <c r="C2" s="29">
-        <f>Assumptions!B23</f>
+        <f>Assumptions!B24</f>
         <v>200</v>
       </c>
       <c r="D2" s="29">
-        <f>Assumptions!B24</f>
+        <f>Assumptions!B25</f>
         <v>300</v>
       </c>
       <c r="E2" s="29">
-        <f>Assumptions!B25</f>
+        <f>Assumptions!B26</f>
         <v>400</v>
       </c>
       <c r="F2" s="29">
-        <f>Assumptions!B26</f>
+        <f>Assumptions!B27</f>
         <v>500</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2708,32 +2719,32 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B4" s="30">
-        <f>650*Assumptions!B22</f>
+        <f>650*Assumptions!B23</f>
         <v>78000</v>
       </c>
       <c r="C4" s="30">
-        <f>670*Assumptions!B23</f>
+        <f>670*Assumptions!B24</f>
         <v>134000</v>
       </c>
       <c r="D4" s="30">
-        <f>690*Assumptions!B24</f>
+        <f>690*Assumptions!B25</f>
         <v>207000</v>
       </c>
       <c r="E4" s="30">
-        <f>710*Assumptions!B25</f>
+        <f>710*Assumptions!B26</f>
         <v>284000</v>
       </c>
       <c r="F4" s="30">
-        <f>732*Assumptions!B26</f>
+        <f>732*Assumptions!B27</f>
         <v>366000</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -2758,7 +2769,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2768,32 +2779,32 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B7" s="30">
-        <f>450*Assumptions!B22</f>
+        <f>450*Assumptions!B23</f>
         <v>54000</v>
       </c>
       <c r="C7" s="30">
-        <f>464*Assumptions!B23</f>
+        <f>464*Assumptions!B24</f>
         <v>92800</v>
       </c>
       <c r="D7" s="30">
-        <f>478*Assumptions!B24</f>
+        <f>478*Assumptions!B25</f>
         <v>143400</v>
       </c>
       <c r="E7" s="30">
-        <f>492*Assumptions!B25</f>
+        <f>492*Assumptions!B26</f>
         <v>196800</v>
       </c>
       <c r="F7" s="30">
-        <f>507*Assumptions!B26</f>
+        <f>507*Assumptions!B27</f>
         <v>253500</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -2818,7 +2829,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2828,7 +2839,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B10" s="30">
         <f>22000*12</f>
@@ -2853,7 +2864,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" s="30">
         <f>3000*12</f>
@@ -2878,7 +2889,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" s="30">
         <v>22000</v>
@@ -2898,7 +2909,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" s="31">
         <f>SUM(B10:B12)</f>
@@ -2923,7 +2934,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2933,7 +2944,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" s="30">
         <v>30000</v>
@@ -2953,7 +2964,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B16" s="30">
         <v>12000</v>
@@ -2973,7 +2984,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B17" s="30">
         <v>18000</v>
@@ -2993,32 +3004,32 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" s="30">
-        <f>750*Assumptions!B22</f>
+        <f>750*Assumptions!B23</f>
         <v>90000</v>
       </c>
       <c r="C18" s="30">
-        <f>773*Assumptions!B23</f>
+        <f>773*Assumptions!B24</f>
         <v>154600</v>
       </c>
       <c r="D18" s="30">
-        <f>796*Assumptions!B24</f>
+        <f>796*Assumptions!B25</f>
         <v>238800</v>
       </c>
       <c r="E18" s="30">
-        <f>820*Assumptions!B25</f>
+        <f>820*Assumptions!B26</f>
         <v>328000</v>
       </c>
       <c r="F18" s="30">
-        <f>845*Assumptions!B26</f>
+        <f>845*Assumptions!B27</f>
         <v>422500</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" s="31">
         <f>SUM(B15:B18)</f>
@@ -3043,7 +3054,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B21" s="31">
         <f>B5+B8+B13+B19</f>
@@ -3093,24 +3104,24 @@
         <v>23</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3120,7 +3131,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B3" s="30">
         <v>46628.6108154935</v>
@@ -3140,7 +3151,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" s="30">
         <v>60000</v>
@@ -3160,7 +3171,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B3:B4)</f>
@@ -3210,24 +3221,24 @@
         <v>1</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B16</f>
@@ -3252,7 +3263,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B26</f>
@@ -3327,7 +3338,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -3352,7 +3363,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -3377,7 +3388,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -3427,13 +3438,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D10" s="40" t="s">
         <v>23</v>
@@ -3460,7 +3471,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3469,7 +3480,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -3479,7 +3490,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3550,134 +3561,117 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="B13" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="28" t="s">
+      <c r="B16" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="C16" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="D16" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="E16" s="28" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="F16" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="29">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="29">
         <f>'Revenue Schedule'!B2</f>
         <v>120</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f>'Revenue Schedule'!C2</f>
         <v>200</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D17" s="29">
         <f>'Revenue Schedule'!D2</f>
         <v>300</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E17" s="29">
         <f>'Revenue Schedule'!E2</f>
         <v>400</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F17" s="29">
         <f>'Revenue Schedule'!F2</f>
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="9" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="44">
-        <f>IF(B16=0,0,(C16-B16)/B16)</f>
+      <c r="B18" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="44">
+        <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D17" s="44">
-        <f>IF(C16=0,0,(D16-C16)/C16)</f>
+      <c r="D18" s="44">
+        <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="44">
-        <f>IF(D16=0,0,(E16-D16)/D16)</f>
+      <c r="E18" s="44">
+        <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="F17" s="44">
-        <f>IF(E16=0,0,(F16-E16)/E16)</f>
+      <c r="F18" s="44">
+        <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="28" t="s">
+      <c r="B20" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="C20" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="D20" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="E20" s="28" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="30">
-        <f>'Financial Model'!B2</f>
-        <v>1465000</v>
-      </c>
-      <c r="C20" s="30">
-        <f>'Financial Model'!C2</f>
-        <v>2328800</v>
-      </c>
-      <c r="D20" s="30">
-        <f>'Financial Model'!D2</f>
-        <v>3452300</v>
-      </c>
-      <c r="E20" s="30">
-        <f>'Financial Model'!E2</f>
-        <v>4623000</v>
-      </c>
-      <c r="F20" s="30">
-        <f>'Financial Model'!F2</f>
-        <v>5891500</v>
+      <c r="F20" s="28" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3685,209 +3679,209 @@
         <v>142</v>
       </c>
       <c r="B21" s="30">
+        <f>'Financial Model'!B2</f>
+        <v>1465000</v>
+      </c>
+      <c r="C21" s="30">
+        <f>'Financial Model'!C2</f>
+        <v>2328800</v>
+      </c>
+      <c r="D21" s="30">
+        <f>'Financial Model'!D2</f>
+        <v>3452300</v>
+      </c>
+      <c r="E21" s="30">
+        <f>'Financial Model'!E2</f>
+        <v>4623000</v>
+      </c>
+      <c r="F21" s="30">
+        <f>'Financial Model'!F2</f>
+        <v>5891500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
         <v>780535</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C22" s="30">
         <f>'Financial Model'!C3</f>
         <v>936642</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D22" s="30">
         <f>'Financial Model'!D3</f>
         <v>936642</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E22" s="30">
         <f>'Financial Model'!E3</f>
         <v>936642</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F22" s="30">
         <f>'Financial Model'!F3</f>
         <v>936642</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B23" s="30">
         <f>'Financial Model'!B4</f>
         <v>604000</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C23" s="30">
         <f>'Financial Model'!C4</f>
         <v>774860</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D23" s="30">
         <f>'Financial Model'!D4</f>
         <v>994470</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E23" s="30">
         <f>'Financial Model'!E4</f>
         <v>1226220</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F23" s="30">
         <f>'Financial Model'!F4</f>
         <v>1471947</v>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="31">
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
         <v>1491164</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="31">
         <f>'Financial Model'!C6</f>
         <v>1778131</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D24" s="31">
         <f>'Financial Model'!D6</f>
         <v>2002741</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E24" s="31">
         <f>'Financial Model'!E6</f>
         <v>2219491</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F24" s="31">
         <f>'Financial Model'!F6</f>
         <v>2465218</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="B24" s="45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" s="45">
         <f>'Financial Model'!B7</f>
         <v>-26164</v>
       </c>
-      <c r="C24" s="46">
+      <c r="C25" s="46">
         <f>'Financial Model'!C7</f>
         <v>550669</v>
       </c>
-      <c r="D24" s="46">
+      <c r="D25" s="46">
         <f>'Financial Model'!D7</f>
         <v>1449559</v>
       </c>
-      <c r="E24" s="46">
+      <c r="E25" s="46">
         <f>'Financial Model'!E7</f>
         <v>2403509</v>
       </c>
-      <c r="F24" s="46">
+      <c r="F25" s="46">
         <f>'Financial Model'!F7</f>
         <v>3426282</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="B25" s="30">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
         <v>-26164</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C26" s="30">
         <f>'Financial Model'!C8</f>
         <v>524505</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D26" s="30">
         <f>'Financial Model'!D8</f>
         <v>1974064</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E26" s="30">
         <f>'Financial Model'!E8</f>
         <v>4377573</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F26" s="30">
         <f>'Financial Model'!F8</f>
         <v>7803855</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="47" t="str">
+      <c r="B27" s="47" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C27" s="13">
         <f>'Financial Model'!C9</f>
         <v>3.5397054547724545</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D27" s="13">
         <f>'Financial Model'!D9</f>
         <v>11.828173488234373</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E27" s="13">
         <f>'Financial Model'!E9</f>
         <v>23.66798333491778</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F27" s="13">
         <f>'Financial Model'!F9</f>
         <v>37.98700966811049</v>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
+    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="30">
-        <f>IF('Revenue Schedule'!B2=0,0,B20/'Revenue Schedule'!B2)</f>
-        <v>12208.333333333334</v>
-      </c>
-      <c r="C29" s="30">
-        <f>IF('Revenue Schedule'!C2=0,0,C20/'Revenue Schedule'!C2)</f>
-        <v>11644</v>
-      </c>
-      <c r="D29" s="30">
-        <f>IF('Revenue Schedule'!D2=0,0,D20/'Revenue Schedule'!D2)</f>
-        <v>11507.666666666666</v>
-      </c>
-      <c r="E29" s="30">
-        <f>IF('Revenue Schedule'!E2=0,0,E20/'Revenue Schedule'!E2)</f>
-        <v>11557.5</v>
-      </c>
-      <c r="F29" s="30">
-        <f>IF('Revenue Schedule'!F2=0,0,F20/'Revenue Schedule'!F2)</f>
-        <v>11783</v>
-      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="44">
-        <f>IF(B20=0,0,'Financial Model'!B3/B20)</f>
-        <v>0.5327883959044368</v>
-      </c>
-      <c r="C30" s="44">
-        <f>IF(C20=0,0,'Financial Model'!C3/C20)</f>
-        <v>0.4021994160082446</v>
-      </c>
-      <c r="D30" s="44">
-        <f>IF(D20=0,0,'Financial Model'!D3/D20)</f>
-        <v>0.2713095617414477</v>
-      </c>
-      <c r="E30" s="44">
-        <f>IF(E20=0,0,'Financial Model'!E3/E20)</f>
-        <v>0.20260480207657366</v>
-      </c>
-      <c r="F30" s="44">
-        <f>IF(F20=0,0,'Financial Model'!F3/F20)</f>
-        <v>0.15898192310956463</v>
+      <c r="B30" s="30">
+        <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
+        <v>12208.333333333334</v>
+      </c>
+      <c r="C30" s="30">
+        <f>IF('Revenue Schedule'!C2=0,0,C21/'Revenue Schedule'!C2)</f>
+        <v>11644</v>
+      </c>
+      <c r="D30" s="30">
+        <f>IF('Revenue Schedule'!D2=0,0,D21/'Revenue Schedule'!D2)</f>
+        <v>11507.666666666666</v>
+      </c>
+      <c r="E30" s="30">
+        <f>IF('Revenue Schedule'!E2=0,0,E21/'Revenue Schedule'!E2)</f>
+        <v>11557.5</v>
+      </c>
+      <c r="F30" s="30">
+        <f>IF('Revenue Schedule'!F2=0,0,F21/'Revenue Schedule'!F2)</f>
+        <v>11783</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3895,99 +3889,104 @@
         <v>157</v>
       </c>
       <c r="B31" s="44">
-        <f>IF(B20=0,0,'Financial Model'!B4/B20)</f>
+        <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
+        <v>0.5327883959044368</v>
+      </c>
+      <c r="C31" s="44">
+        <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
+        <v>0.4021994160082446</v>
+      </c>
+      <c r="D31" s="44">
+        <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
+        <v>0.2713095617414477</v>
+      </c>
+      <c r="E31" s="44">
+        <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
+        <v>0.20260480207657366</v>
+      </c>
+      <c r="F31" s="44">
+        <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
+        <v>0.15898192310956463</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" s="44">
+        <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.41228668941979524</v>
       </c>
-      <c r="C31" s="44">
-        <f>IF(C20=0,0,'Financial Model'!C4/C20)</f>
+      <c r="C32" s="44">
+        <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.3327293026451391</v>
       </c>
-      <c r="D31" s="44">
-        <f>IF(D20=0,0,'Financial Model'!D4/D20)</f>
+      <c r="D32" s="44">
+        <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.2880601338238276</v>
       </c>
-      <c r="E31" s="44">
-        <f>IF(E20=0,0,'Financial Model'!E4/E20)</f>
+      <c r="E32" s="44">
+        <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.26524334847501624</v>
       </c>
-      <c r="F31" s="44">
-        <f>IF(F20=0,0,'Financial Model'!F4/F20)</f>
+      <c r="F32" s="44">
+        <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.24984248493592465</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="B32" s="48">
-        <f>IF(B20=0,0,B24/B20)</f>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" s="48">
+        <f>IF(B21=0,0,B25/B21)</f>
         <v>-0.01785938566552901</v>
       </c>
-      <c r="C32" s="12">
-        <f>IF(C20=0,0,C24/C20)</f>
+      <c r="C33" s="12">
+        <f>IF(C21=0,0,C25/C21)</f>
         <v>0.23646040879422878</v>
       </c>
-      <c r="D32" s="12">
-        <f>IF(D20=0,0,D24/D20)</f>
+      <c r="D33" s="12">
+        <f>IF(D21=0,0,D25/D21)</f>
         <v>0.41988210758045363</v>
       </c>
-      <c r="E32" s="12">
-        <f>IF(E20=0,0,E24/E20)</f>
+      <c r="E33" s="12">
+        <f>IF(E21=0,0,E25/E21)</f>
         <v>0.5199024443002379</v>
       </c>
-      <c r="F32" s="12">
-        <f>IF(F20=0,0,F24/F20)</f>
+      <c r="F33" s="12">
+        <f>IF(F21=0,0,F25/F21)</f>
         <v>0.5815636085886446</v>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B35" s="44">
-        <v>0.032764505119453925</v>
-      </c>
-      <c r="C35" s="44">
-        <v>0.03538302988663689</v>
-      </c>
-      <c r="D35" s="44">
-        <v>0.03684500188280277</v>
-      </c>
-      <c r="E35" s="44">
-        <v>0.03781094527363184</v>
-      </c>
-      <c r="F35" s="44">
-        <v>0.03819061359585844</v>
-      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
         <v>161</v>
       </c>
       <c r="B36" s="44">
-        <v>0.8477815699658703</v>
+        <v>0.032764505119453925</v>
       </c>
       <c r="C36" s="44">
-        <v>0.9066472002748196</v>
+        <v>0.03538302988663689</v>
       </c>
       <c r="D36" s="44">
-        <v>0.9356371114908901</v>
+        <v>0.03684500188280277</v>
       </c>
       <c r="E36" s="44">
-        <v>0.9502920181700195</v>
+        <v>0.03781094527363184</v>
       </c>
       <c r="F36" s="44">
-        <v>0.9507765424764492</v>
+        <v>0.03819061359585844</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3995,18 +3994,38 @@
         <v>162</v>
       </c>
       <c r="B37" s="44">
+        <v>0.8477815699658703</v>
+      </c>
+      <c r="C37" s="44">
+        <v>0.9066472002748196</v>
+      </c>
+      <c r="D37" s="44">
+        <v>0.9356371114908901</v>
+      </c>
+      <c r="E37" s="44">
+        <v>0.9502920181700195</v>
+      </c>
+      <c r="F37" s="44">
+        <v>0.9507765424764492</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="B38" s="44">
         <v>0.11945392491467577</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C38" s="44">
         <v>0.057969769838543454</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D38" s="44">
         <v>0.0275178866263071</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E38" s="44">
         <v>0.01189703655634869</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F38" s="44">
         <v>0.011032843927692439</v>
       </c>
     </row>
@@ -4220,7 +4239,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
@@ -4231,7 +4250,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
@@ -4242,41 +4261,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C7" s="54">
         <v>120</v>
@@ -4296,7 +4315,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" s="55">
         <v>1465000</v>
@@ -4316,7 +4335,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="55">
         <v>780535</v>
@@ -4356,7 +4375,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C11" s="55">
         <v>46628.6108154935</v>
@@ -4376,7 +4395,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="57">
         <v>-26164</v>
@@ -4396,7 +4415,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="56" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C13" s="57">
         <v>-26164</v>
@@ -4416,7 +4435,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="59">
         <v>-0.01785938566552901</v>
@@ -4436,7 +4455,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" s="61">
         <v>12208.333333333334</v>
@@ -4454,12 +4473,12 @@
         <v>11783</v>
       </c>
       <c r="H15" s="62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="56" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="63">
         <v>11926.363423462444</v>
@@ -4479,7 +4498,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C17" s="55">
         <v>650</v>
@@ -4499,7 +4518,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18" s="64">
         <v>2683.3333333333335</v>
@@ -4517,12 +4536,12 @@
         <v>724.8386516800001</v>
       </c>
       <c r="H18" s="62" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="56" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C19" s="65">
         <v>-218.03333333333333</v>
@@ -4542,7 +4561,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C20" s="60">
         <v>0.5327883959044368</v>
@@ -4560,12 +4579,12 @@
         <v>0.15898192310956463</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C21" s="67">
         <v>0.2197952218430034</v>
@@ -4583,12 +4602,12 @@
         <v>0.06151562859034203</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" s="67">
         <v>0.05492491467576792</v>
@@ -4606,12 +4625,12 @@
         <v>0.5911755919545107</v>
       </c>
       <c r="H22" s="62" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="56" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="68">
         <v>3</v>
@@ -4629,12 +4648,12 @@
         <v>3</v>
       </c>
       <c r="H23" s="62" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="56" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C24" s="69">
         <v>1.7256572433263127</v>
@@ -4652,12 +4671,12 @@
         <v>74.69471938123272</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C25" s="70" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
@@ -4680,12 +4699,12 @@
         <v>0</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C26" s="71">
         <v>0</v>
@@ -4703,12 +4722,12 @@
         <v>38</v>
       </c>
       <c r="H26" s="62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C27" s="71">
         <v>0</v>
@@ -4726,141 +4745,141 @@
         <v>1160</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="73" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D30" s="74" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E30" s="74"/>
       <c r="F30" s="75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G30" s="75"/>
       <c r="H30" s="75"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="73" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C31" s="76" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D31" s="74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E31" s="74"/>
       <c r="F31" s="75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G31" s="75"/>
       <c r="H31" s="75"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="73" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D32" s="74" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E32" s="74"/>
       <c r="F32" s="75" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G32" s="75"/>
       <c r="H32" s="75"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="73" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D33" s="74" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E33" s="74"/>
       <c r="F33" s="75" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G33" s="75"/>
       <c r="H33" s="75"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="73" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D34" s="74" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E34" s="74"/>
       <c r="F34" s="75" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G34" s="75"/>
       <c r="H34" s="75"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="73" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D35" s="74" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E35" s="74"/>
       <c r="F35" s="75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G35" s="75"/>
       <c r="H35" s="75"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="73" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D36" s="74" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E36" s="74"/>
       <c r="F36" s="75" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G36" s="75"/>
       <c r="H36" s="75"/>
@@ -4870,7 +4889,7 @@
         <v>20</v>
       </c>
       <c r="C38" s="56" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D38" s="56"/>
       <c r="E38" s="56"/>
@@ -4878,7 +4897,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="77" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C40" s="77"/>
       <c r="D40" s="77"/>
@@ -4992,10 +5011,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -546,7 +546,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -546,7 +546,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -666,7 +666,7 @@
     <t>The model reaches net income early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1909,7 +1909,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1919,7 +1919,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="42" t="s">
         <v>167</v>
       </c>
@@ -1929,8 +1929,9 @@
       <c r="F2" s="42"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="42"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="51" t="s">
         <v>168</v>
       </c>
@@ -1940,6 +1941,7 @@
       <c r="F3" s="51"/>
       <c r="G3" s="51"/>
       <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="52" t="s">
@@ -2430,7 +2432,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
         <v>201</v>
       </c>
@@ -2446,8 +2448,9 @@
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="75" t="s">
         <v>205</v>
       </c>
@@ -2463,8 +2466,9 @@
       </c>
       <c r="G30" s="77"/>
       <c r="H30" s="77"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="77"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="75" t="s">
         <v>209</v>
       </c>
@@ -2480,8 +2484,9 @@
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="77"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="75" t="s">
         <v>213</v>
       </c>
@@ -2497,8 +2502,9 @@
       </c>
       <c r="G32" s="77"/>
       <c r="H32" s="77"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="77"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="75" t="s">
         <v>216</v>
       </c>
@@ -2514,8 +2520,9 @@
       </c>
       <c r="G33" s="77"/>
       <c r="H33" s="77"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="77"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="75" t="s">
         <v>219</v>
       </c>
@@ -2531,8 +2538,9 @@
       </c>
       <c r="G34" s="77"/>
       <c r="H34" s="77"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="77"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="75" t="s">
         <v>222</v>
       </c>
@@ -2548,8 +2556,9 @@
       </c>
       <c r="G35" s="77"/>
       <c r="H35" s="77"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="77"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="75" t="s">
         <v>225</v>
       </c>
@@ -2565,6 +2574,7 @@
       </c>
       <c r="G36" s="77"/>
       <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="75" t="s">
@@ -2577,7 +2587,7 @@
       <c r="E38" s="58"/>
       <c r="F38" s="58"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="79" t="s">
         <v>229</v>
       </c>
@@ -2587,29 +2597,30 @@
       <c r="F40" s="79"/>
       <c r="G40" s="79"/>
       <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Standard_Export_Charter_ADA_Grade-Band.xlsx
@@ -20,19 +20,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Revenue Schedule'!$A1:$F16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue Schedule'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Staffing &amp; Personnel'!$A1:$H34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Staffing &amp; Personnel'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Operating Expenses'!$A1:$F21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Capital &amp; Debt'!$A1:$F5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Capital &amp; Debt'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$F10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A1:$G16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Financial Model'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Decision History'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Financial Health'!$A1:$I41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="243">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>May 7, 2026</t>
+    <t>May 9, 2026</t>
   </si>
   <si>
     <t>KEY HIGHLIGHTS</t>
@@ -405,6 +405,27 @@
     <t>Total Personnel Cost</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION</t>
+  </si>
+  <si>
+    <t>5-Year Total</t>
+  </si>
+  <si>
+    <t>Founder Compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Fully-loaded (incl. benefits + payroll tax)</t>
+  </si>
+  <si>
+    <t>Founder Compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t>Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market rate ("sweat equity"). Lenders and boards underwrite to the market-rate line; the adjustment shows the gap.</t>
+  </si>
+  <si>
     <t>INSTRUCTIONAL / PROGRAM</t>
   </si>
   <si>
@@ -486,6 +507,21 @@
     <t>Cumulative Net Income</t>
   </si>
   <si>
+    <t>FOUNDER COMPENSATION (memo — already in Personnel above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (as planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Founder compensation (market rate, normalized)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Lender Normalization Adjustment (market - planned)</t>
+  </si>
+  <si>
+    <t>Note: Founder is paying themselves below market ("sweat equity"). Lenders / boards underwrite to the market-rate line.</t>
+  </si>
+  <si>
     <t>Break-even</t>
   </si>
   <si>
@@ -546,7 +582,10 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
+  </si>
+  <si>
+    <t>Built from assumptions</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -745,7 +784,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -843,6 +882,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="16"/>
@@ -876,6 +921,13 @@
       <i/>
       <color rgb="FF6B7280"/>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -991,7 +1043,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1033,6 +1085,12 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1040,23 +1098,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="20" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="166" fontId="21" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1082,7 +1141,7 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1117,10 +1176,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1909,7 +1968,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I40"/>
+  <dimension ref="B2:I41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1920,691 +1979,702 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="B2" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="55" t="s">
+      <c r="B3" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5" s="57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D7" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E7" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F7" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G7" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="55" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="56">
-        <v>120</v>
-      </c>
-      <c r="D7" s="56">
-        <v>200</v>
-      </c>
-      <c r="E7" s="56">
-        <v>300</v>
-      </c>
-      <c r="F7" s="56">
-        <v>400</v>
-      </c>
-      <c r="G7" s="56">
-        <v>500</v>
+      <c r="H7" s="58" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="57">
-        <v>1465000</v>
-      </c>
-      <c r="D8" s="57">
-        <v>2328800</v>
-      </c>
-      <c r="E8" s="57">
-        <v>3452300</v>
-      </c>
-      <c r="F8" s="57">
-        <v>4623000</v>
-      </c>
-      <c r="G8" s="57">
-        <v>5891500</v>
+        <v>187</v>
+      </c>
+      <c r="C8" s="59">
+        <v>120</v>
+      </c>
+      <c r="D8" s="59">
+        <v>200</v>
+      </c>
+      <c r="E8" s="59">
+        <v>300</v>
+      </c>
+      <c r="F8" s="59">
+        <v>400</v>
+      </c>
+      <c r="G8" s="59">
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="57">
-        <v>780535</v>
-      </c>
-      <c r="D9" s="57">
-        <v>936642</v>
-      </c>
-      <c r="E9" s="57">
-        <v>936642</v>
-      </c>
-      <c r="F9" s="57">
-        <v>936642</v>
-      </c>
-      <c r="G9" s="57">
-        <v>936642</v>
+        <v>188</v>
+      </c>
+      <c r="C9" s="60">
+        <v>1465000</v>
+      </c>
+      <c r="D9" s="60">
+        <v>2328800</v>
+      </c>
+      <c r="E9" s="60">
+        <v>3452300</v>
+      </c>
+      <c r="F9" s="60">
+        <v>4623000</v>
+      </c>
+      <c r="G9" s="60">
+        <v>5891500</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="57">
-        <v>604000</v>
-      </c>
-      <c r="D10" s="57">
-        <v>774860</v>
-      </c>
-      <c r="E10" s="57">
-        <v>994470</v>
-      </c>
-      <c r="F10" s="57">
-        <v>1226220</v>
-      </c>
-      <c r="G10" s="57">
-        <v>1471947</v>
+        <v>189</v>
+      </c>
+      <c r="C10" s="60">
+        <v>780535</v>
+      </c>
+      <c r="D10" s="60">
+        <v>936642</v>
+      </c>
+      <c r="E10" s="60">
+        <v>936642</v>
+      </c>
+      <c r="F10" s="60">
+        <v>936642</v>
+      </c>
+      <c r="G10" s="60">
+        <v>936642</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="57">
+        <v>17</v>
+      </c>
+      <c r="C11" s="60">
+        <v>604000</v>
+      </c>
+      <c r="D11" s="60">
+        <v>774860</v>
+      </c>
+      <c r="E11" s="60">
+        <v>994470</v>
+      </c>
+      <c r="F11" s="60">
+        <v>1226220</v>
+      </c>
+      <c r="G11" s="60">
+        <v>1471947</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="60">
         <v>46628.6108154935</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D12" s="60">
         <v>46628.6108154935</v>
       </c>
-      <c r="E11" s="57">
+      <c r="E12" s="60">
         <v>46628.6108154935</v>
       </c>
-      <c r="F11" s="57">
+      <c r="F12" s="60">
         <v>46628.6108154935</v>
       </c>
-      <c r="G11" s="57">
+      <c r="G12" s="60">
         <v>46628.6108154935</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="59">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="61" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="62">
         <v>-26164</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D13" s="63">
         <v>550669</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E13" s="63">
         <v>1449559</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F13" s="63">
         <v>2403509</v>
       </c>
-      <c r="G12" s="60">
+      <c r="G13" s="63">
         <v>3426282</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="58" t="s">
-        <v>178</v>
-      </c>
-      <c r="C13" s="59">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" s="62">
         <v>-26164</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D14" s="63">
         <v>524505</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E14" s="63">
         <v>1974064</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F14" s="63">
         <v>4377573</v>
       </c>
-      <c r="G13" s="60">
+      <c r="G14" s="63">
         <v>7803855</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="58" t="s">
-        <v>179</v>
-      </c>
-      <c r="C14" s="61">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" s="64">
         <v>-0.01785938566552901</v>
       </c>
-      <c r="D14" s="62">
+      <c r="D15" s="65">
         <v>0.23646040879422878</v>
       </c>
-      <c r="E14" s="62">
+      <c r="E15" s="65">
         <v>0.41988210758045363</v>
       </c>
-      <c r="F14" s="62">
+      <c r="F15" s="65">
         <v>0.5199024443002379</v>
       </c>
-      <c r="G14" s="62">
+      <c r="G15" s="65">
         <v>0.5815636085886446</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="58" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" s="63">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="61" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="66">
         <v>12208.333333333334</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D16" s="66">
         <v>11644</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E16" s="66">
         <v>11507.666666666666</v>
       </c>
-      <c r="F15" s="63">
+      <c r="F16" s="66">
         <v>11557.5</v>
       </c>
-      <c r="G15" s="63">
+      <c r="G16" s="66">
         <v>11783</v>
       </c>
-      <c r="H15" s="64" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="58" t="s">
-        <v>181</v>
-      </c>
-      <c r="C16" s="65">
+      <c r="H16" s="67" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="68">
         <v>11926.363423462444</v>
       </c>
-      <c r="D16" s="65">
+      <c r="D17" s="68">
         <v>8790.653054077467</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E17" s="68">
         <v>6592.468702718311</v>
       </c>
-      <c r="F16" s="65">
+      <c r="F17" s="68">
         <v>5523.726527038733</v>
       </c>
-      <c r="G16" s="65">
+      <c r="G17" s="68">
         <v>4910.435221630987</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" s="57">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C18" s="60">
         <v>650</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D18" s="60">
         <v>670</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E18" s="60">
         <v>690</v>
       </c>
-      <c r="F17" s="57">
+      <c r="F18" s="60">
         <v>710</v>
       </c>
-      <c r="G17" s="57">
+      <c r="G18" s="60">
         <v>732</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C18" s="66">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="69">
         <v>2683.3333333333335</v>
       </c>
-      <c r="D18" s="63">
+      <c r="D19" s="66">
         <v>1658.3</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E19" s="66">
         <v>1138.712</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F19" s="66">
         <v>879.6398199999999</v>
       </c>
-      <c r="G18" s="63">
+      <c r="G19" s="66">
         <v>724.8386516800001</v>
       </c>
-      <c r="H18" s="64" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="58" t="s">
-        <v>185</v>
-      </c>
-      <c r="C19" s="67">
+      <c r="H19" s="67" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="61" t="s">
+        <v>198</v>
+      </c>
+      <c r="C20" s="70">
         <v>-218.03333333333333</v>
       </c>
-      <c r="D19" s="68">
+      <c r="D20" s="71">
         <v>2753.345</v>
       </c>
-      <c r="E19" s="68">
+      <c r="E20" s="71">
         <v>4831.863333333334</v>
       </c>
-      <c r="F19" s="68">
+      <c r="F20" s="71">
         <v>6008.7725</v>
       </c>
-      <c r="G19" s="68">
+      <c r="G20" s="71">
         <v>6852.564</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="58" t="s">
-        <v>186</v>
-      </c>
-      <c r="C20" s="62">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="61" t="s">
+        <v>199</v>
+      </c>
+      <c r="C21" s="65">
         <v>0.5327883959044368</v>
       </c>
-      <c r="D20" s="62">
+      <c r="D21" s="65">
         <v>0.4021994160082446</v>
       </c>
-      <c r="E20" s="62">
+      <c r="E21" s="65">
         <v>0.2713095617414477</v>
       </c>
-      <c r="F20" s="62">
+      <c r="F21" s="65">
         <v>0.20260480207657366</v>
       </c>
-      <c r="G20" s="62">
+      <c r="G21" s="65">
         <v>0.15898192310956463</v>
       </c>
-      <c r="H20" s="64" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="C21" s="69">
+      <c r="H21" s="67" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="72">
         <v>0.2197952218430034</v>
       </c>
-      <c r="D21" s="62">
+      <c r="D22" s="65">
         <v>0.1424166952937135</v>
       </c>
-      <c r="E21" s="62">
+      <c r="E22" s="65">
         <v>0.0989524664716276</v>
       </c>
-      <c r="F21" s="62">
+      <c r="F22" s="65">
         <v>0.07610986978152713</v>
       </c>
-      <c r="G21" s="62">
+      <c r="G22" s="65">
         <v>0.06151562859034203</v>
       </c>
-      <c r="H21" s="64" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="69">
+      <c r="H22" s="67" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="72">
         <v>0.05492491467576792</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D23" s="65">
         <v>0.2650712813466163</v>
       </c>
-      <c r="E22" s="62">
+      <c r="E23" s="65">
         <v>0.4406303044347247</v>
       </c>
-      <c r="F22" s="62">
+      <c r="F23" s="65">
         <v>0.5321518494484101</v>
       </c>
-      <c r="G22" s="62">
+      <c r="G23" s="65">
         <v>0.5911755919545107</v>
       </c>
-      <c r="H22" s="64" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="58" t="s">
-        <v>192</v>
-      </c>
-      <c r="C23" s="70">
+      <c r="H23" s="67" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="C24" s="73">
         <v>3</v>
       </c>
-      <c r="D23" s="70">
+      <c r="D24" s="73">
         <v>3</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E24" s="73">
         <v>3</v>
       </c>
-      <c r="F23" s="70">
+      <c r="F24" s="73">
         <v>3</v>
       </c>
-      <c r="G23" s="70">
+      <c r="G24" s="73">
         <v>3</v>
       </c>
-      <c r="H23" s="64" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="58" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" s="71">
+      <c r="H24" s="67" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="74">
         <v>1.7256572433263127</v>
       </c>
-      <c r="D24" s="71">
+      <c r="D25" s="74">
         <v>13.238610140941356</v>
       </c>
-      <c r="E24" s="71">
+      <c r="E25" s="74">
         <v>32.62348959996355</v>
       </c>
-      <c r="F24" s="71">
+      <c r="F25" s="74">
         <v>52.76026793366443</v>
       </c>
-      <c r="G24" s="71">
+      <c r="G25" s="74">
         <v>74.69471938123272</v>
       </c>
-      <c r="H24" s="64" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="58" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="72" t="str">
+      <c r="H25" s="67" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="C26" s="75" t="str">
         <f>IF('Financial Model'!B8&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="41" t="str">
+      <c r="D26" s="43" t="str">
         <f>IF(AND('Financial Model'!C8&gt;=0,'Financial Model'!B8&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E25" s="72" t="str">
+      <c r="E26" s="75" t="str">
         <f>IF(AND('Financial Model'!D8&gt;=0,'Financial Model'!C8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="72" t="str">
+      <c r="F26" s="75" t="str">
         <f>IF(AND('Financial Model'!E8&gt;=0,'Financial Model'!D8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="72" t="str">
+      <c r="G26" s="75" t="str">
         <f>IF(AND('Financial Model'!F8&gt;=0,'Financial Model'!E8&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="64" t="s">
+      <c r="H26" s="67" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="58" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="73">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="76">
         <v>0</v>
       </c>
-      <c r="D26" s="73">
+      <c r="D27" s="76">
         <v>4</v>
       </c>
-      <c r="E26" s="74">
+      <c r="E27" s="77">
         <v>12</v>
       </c>
-      <c r="F26" s="70">
+      <c r="F27" s="73">
         <v>24</v>
       </c>
-      <c r="G26" s="70">
+      <c r="G27" s="73">
         <v>38</v>
       </c>
-      <c r="H26" s="64" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="73">
+      <c r="H27" s="67" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="C28" s="76">
         <v>0</v>
       </c>
-      <c r="D27" s="70">
+      <c r="D28" s="73">
         <v>109</v>
       </c>
-      <c r="E27" s="70">
+      <c r="E28" s="73">
         <v>364</v>
       </c>
-      <c r="F27" s="70">
+      <c r="F28" s="73">
         <v>723</v>
       </c>
-      <c r="G27" s="70">
+      <c r="G28" s="73">
         <v>1160</v>
       </c>
-      <c r="H27" s="64" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="75" t="s">
-        <v>205</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77" t="s">
-        <v>208</v>
-      </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
+      <c r="H28" s="67" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="75" t="s">
-        <v>209</v>
-      </c>
-      <c r="C31" s="78" t="s">
-        <v>210</v>
-      </c>
-      <c r="D31" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77" t="s">
-        <v>212</v>
-      </c>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="77"/>
+      <c r="B31" s="78" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D31" s="79" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="79"/>
+      <c r="F31" s="80" t="s">
+        <v>221</v>
+      </c>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="75" t="s">
-        <v>213</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="E32" s="76"/>
-      <c r="F32" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
+      <c r="B32" s="78" t="s">
+        <v>222</v>
+      </c>
+      <c r="C32" s="81" t="s">
+        <v>223</v>
+      </c>
+      <c r="D32" s="79" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="79"/>
+      <c r="F32" s="80" t="s">
+        <v>225</v>
+      </c>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="75" t="s">
-        <v>216</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D33" s="76" t="s">
-        <v>217</v>
-      </c>
-      <c r="E33" s="76"/>
-      <c r="F33" s="77" t="s">
-        <v>218</v>
-      </c>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
+      <c r="B33" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" s="79" t="s">
+        <v>227</v>
+      </c>
+      <c r="E33" s="79"/>
+      <c r="F33" s="80" t="s">
+        <v>228</v>
+      </c>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="75" t="s">
+      <c r="B34" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="C34" s="43" t="s">
         <v>219</v>
       </c>
-      <c r="C34" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D34" s="76" t="s">
-        <v>220</v>
-      </c>
-      <c r="E34" s="76"/>
-      <c r="F34" s="77" t="s">
-        <v>221</v>
-      </c>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
-      <c r="I34" s="77"/>
+      <c r="D34" s="79" t="s">
+        <v>230</v>
+      </c>
+      <c r="E34" s="79"/>
+      <c r="F34" s="80" t="s">
+        <v>231</v>
+      </c>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="80"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="75" t="s">
-        <v>222</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D35" s="76" t="s">
-        <v>223</v>
-      </c>
-      <c r="E35" s="76"/>
-      <c r="F35" s="77" t="s">
-        <v>224</v>
-      </c>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
+      <c r="B35" s="78" t="s">
+        <v>232</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D35" s="79" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" s="79"/>
+      <c r="F35" s="80" t="s">
+        <v>234</v>
+      </c>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
+      <c r="I35" s="80"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="75" t="s">
-        <v>225</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>206</v>
-      </c>
-      <c r="D36" s="76" t="s">
-        <v>226</v>
-      </c>
-      <c r="E36" s="76"/>
-      <c r="F36" s="77" t="s">
-        <v>227</v>
-      </c>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="75" t="s">
+      <c r="B36" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D36" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="E36" s="79"/>
+      <c r="F36" s="80" t="s">
+        <v>237</v>
+      </c>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
+    </row>
+    <row r="37" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="78" t="s">
+        <v>238</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D37" s="79" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" s="79"/>
+      <c r="F37" s="80" t="s">
+        <v>240</v>
+      </c>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="58" t="s">
-        <v>228</v>
-      </c>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="79" t="s">
-        <v>229</v>
-      </c>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
+      <c r="C39" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="82"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
@@ -2619,95 +2689,97 @@
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="F36:I36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B41:I41"/>
   </mergeCells>
-  <conditionalFormatting sqref="C12:G12">
+  <conditionalFormatting sqref="C13:G13">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C12&gt;=0</formula>
+      <formula>C13&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C12&gt;=-1</formula>
+      <formula>C13&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C12&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13:G13">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C13&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C13&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C13&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:G14">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C14&gt;=0.05</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>C14&gt;=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C14&lt;0</formula>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C14&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C14&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C15&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C15&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C15&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&gt;=10000</formula>
+      <formula>C16&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&gt;=7000</formula>
+      <formula>C16&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&lt;7000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:G21">
-    <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C21&lt;=0.55</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C21&lt;=0.65</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C21&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:G22">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C22&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C22&lt;=0.22</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C22&gt;0.22</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23:G23">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C23&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C23&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C23&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C25:G25">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C25&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1.15</formula>
+      <formula>C25&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1.15</formula>
+      <formula>C25&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3061,11 +3133,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3477,9 +3549,154 @@
         <v>936642</v>
       </c>
     </row>
+    <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="30">
+        <v>105000</v>
+      </c>
+      <c r="C29" s="30">
+        <v>105000</v>
+      </c>
+      <c r="D29" s="30">
+        <v>105000</v>
+      </c>
+      <c r="E29" s="30">
+        <v>105000</v>
+      </c>
+      <c r="F29" s="30">
+        <v>105000</v>
+      </c>
+      <c r="G29" s="30">
+        <f>SUM(B29:F29)</f>
+        <v>525000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="30">
+        <v>140333</v>
+      </c>
+      <c r="C30" s="30">
+        <v>140333</v>
+      </c>
+      <c r="D30" s="30">
+        <v>140333</v>
+      </c>
+      <c r="E30" s="30">
+        <v>140333</v>
+      </c>
+      <c r="F30" s="30">
+        <v>140333</v>
+      </c>
+      <c r="G30" s="30">
+        <f>SUM(B30:F30)</f>
+        <v>701665</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="30">
+        <v>95000</v>
+      </c>
+      <c r="C31" s="30">
+        <v>120000</v>
+      </c>
+      <c r="D31" s="30">
+        <v>150000</v>
+      </c>
+      <c r="E31" s="30">
+        <v>150000</v>
+      </c>
+      <c r="F31" s="30">
+        <v>185000</v>
+      </c>
+      <c r="G31" s="30">
+        <f>SUM(B31:F31)</f>
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="30">
+        <v>126968</v>
+      </c>
+      <c r="C32" s="30">
+        <v>160380</v>
+      </c>
+      <c r="D32" s="30">
+        <v>200475</v>
+      </c>
+      <c r="E32" s="30">
+        <v>200475</v>
+      </c>
+      <c r="F32" s="30">
+        <v>247253</v>
+      </c>
+      <c r="G32" s="30">
+        <f>SUM(B32:F32)</f>
+        <v>935551</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="10">
+        <v>-13365</v>
+      </c>
+      <c r="C33" s="10">
+        <v>20048</v>
+      </c>
+      <c r="D33" s="10">
+        <v>60143</v>
+      </c>
+      <c r="E33" s="10">
+        <v>60143</v>
+      </c>
+      <c r="F33" s="10">
+        <v>106920</v>
+      </c>
+      <c r="G33" s="10">
+        <f>SUM(B33:F33)</f>
+        <v>233889</v>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3549,7 +3766,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3559,7 +3776,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B4" s="30">
         <f>650*Assumptions!B23</f>
@@ -3584,7 +3801,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B4:B4)</f>
@@ -3609,7 +3826,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3619,7 +3836,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B7" s="30">
         <f>450*Assumptions!B23</f>
@@ -3644,7 +3861,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B7:B7)</f>
@@ -3669,7 +3886,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3679,7 +3896,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B10" s="30">
         <f>22000*12</f>
@@ -3704,7 +3921,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B11" s="30">
         <f>3000*12</f>
@@ -3729,7 +3946,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B12" s="30">
         <v>22000</v>
@@ -3749,7 +3966,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B13" s="31">
         <f>SUM(B10:B12)</f>
@@ -3774,7 +3991,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3784,7 +4001,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B15" s="30">
         <v>30000</v>
@@ -3804,7 +4021,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B16" s="30">
         <v>12000</v>
@@ -3824,7 +4041,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B17" s="30">
         <v>18000</v>
@@ -3844,7 +4061,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B18" s="30">
         <f>750*Assumptions!B23</f>
@@ -3869,7 +4086,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B19" s="31">
         <f>SUM(B15:B18)</f>
@@ -3894,7 +4111,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B21" s="31">
         <f>B5+B8+B13+B19</f>
@@ -3961,7 +4178,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3971,7 +4188,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B3" s="30">
         <v>46628.6108154935</v>
@@ -3991,7 +4208,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B4" s="30">
         <v>60000</v>
@@ -4011,7 +4228,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B5" s="31">
         <f>SUM(B3:B4)</f>
@@ -4049,11 +4266,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4078,7 +4295,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B2" s="30">
         <f>'Revenue Schedule'!B16</f>
@@ -4103,7 +4320,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B3" s="30">
         <f>'Staffing &amp; Personnel'!B26</f>
@@ -4178,7 +4395,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B6" s="31">
         <f>B3+B4+B5</f>
@@ -4203,7 +4420,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B7" s="31">
         <f>B2-B6</f>
@@ -4228,7 +4445,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B8" s="30">
         <f>B7</f>
@@ -4255,48 +4472,147 @@
       <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="39" t="str">
+      <c r="B9" s="41" t="str">
         <f>IF(B6=0,0,IF(B8&gt;0,B8/(B6/12),0))</f>
         <v>0</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="41">
         <f>IF(C6=0,0,IF(C8&gt;0,C8/(C6/12),0))</f>
         <v>3.5397054547724545</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="41">
         <f>IF(D6=0,0,IF(D8&gt;0,D8/(D6/12),0))</f>
         <v>11.828173488234373</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="41">
         <f>IF(E6=0,0,IF(E8&gt;0,E8/(E6/12),0))</f>
         <v>23.66798333491778</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="41">
         <f>IF(F6=0,0,IF(F8&gt;0,F8/(F6/12),0))</f>
         <v>37.98700966811049</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="40" t="s">
+    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="30">
+        <v>140333</v>
+      </c>
+      <c r="C12" s="30">
+        <v>140333</v>
+      </c>
+      <c r="D12" s="30">
+        <v>140333</v>
+      </c>
+      <c r="E12" s="30">
+        <v>140333</v>
+      </c>
+      <c r="F12" s="30">
+        <v>140333</v>
+      </c>
+      <c r="G12" s="30">
+        <f>SUM(B12:F12)</f>
+        <v>701665</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="30">
+        <v>126968</v>
+      </c>
+      <c r="C13" s="30">
+        <v>160380</v>
+      </c>
+      <c r="D13" s="30">
+        <v>200475</v>
+      </c>
+      <c r="E13" s="30">
+        <v>200475</v>
+      </c>
+      <c r="F13" s="30">
+        <v>247253</v>
+      </c>
+      <c r="G13" s="30">
+        <f>SUM(B13:F13)</f>
+        <v>935551</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="10">
+        <v>-13365</v>
+      </c>
+      <c r="C14" s="10">
+        <v>20048</v>
+      </c>
+      <c r="D14" s="10">
+        <v>60143</v>
+      </c>
+      <c r="E14" s="10">
+        <v>60143</v>
+      </c>
+      <c r="F14" s="10">
+        <v>106920</v>
+      </c>
+      <c r="G14" s="10">
+        <f>SUM(B14:F14)</f>
+        <v>233889</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="40" t="s">
+      <c r="C16" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E16" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F16" s="42" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -4319,18 +4635,18 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="A1" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>151</v>
+      <c r="A2" s="45" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4412,12 +4728,12 @@
         <v>41</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -4472,24 +4788,24 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C18" s="44">
+        <v>167</v>
+      </c>
+      <c r="C18" s="46">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
         <v>0.6666666666666666</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="46">
         <f>IF(C17=0,0,(D17-C17)/C17)</f>
         <v>0.5</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="46">
         <f>IF(D17=0,0,(E17-D17)/D17)</f>
         <v>0.3333333333333333</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="46">
         <f>IF(E17=0,0,(F17-E17)/E17)</f>
         <v>0.25</v>
       </c>
@@ -4516,7 +4832,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B21" s="30">
         <f>'Financial Model'!B2</f>
@@ -4541,7 +4857,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B22" s="30">
         <f>'Financial Model'!B3</f>
@@ -4591,7 +4907,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B24" s="31">
         <f>'Financial Model'!B6</f>
@@ -4616,32 +4932,32 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25" s="45">
+        <v>153</v>
+      </c>
+      <c r="B25" s="47">
         <f>'Financial Model'!B7</f>
         <v>-26164</v>
       </c>
-      <c r="C25" s="46">
+      <c r="C25" s="48">
         <f>'Financial Model'!C7</f>
         <v>550669</v>
       </c>
-      <c r="D25" s="46">
+      <c r="D25" s="48">
         <f>'Financial Model'!D7</f>
         <v>1449559</v>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="48">
         <f>'Financial Model'!E7</f>
         <v>2403509</v>
       </c>
-      <c r="F25" s="46">
+      <c r="F25" s="48">
         <f>'Financial Model'!F7</f>
         <v>3426282</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B26" s="30">
         <f>'Financial Model'!B8</f>
@@ -4668,7 +4984,7 @@
       <c r="A27" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="47" t="str">
+      <c r="B27" s="49" t="str">
         <f>'Financial Model'!B9</f>
         <v>0</v>
       </c>
@@ -4691,7 +5007,7 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -4701,7 +5017,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B30" s="30">
         <f>IF('Revenue Schedule'!B2=0,0,B21/'Revenue Schedule'!B2)</f>
@@ -4726,59 +5042,59 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B31" s="44">
+        <v>170</v>
+      </c>
+      <c r="B31" s="46">
         <f>IF(B21=0,0,'Financial Model'!B3/B21)</f>
         <v>0.5327883959044368</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="46">
         <f>IF(C21=0,0,'Financial Model'!C3/C21)</f>
         <v>0.4021994160082446</v>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="46">
         <f>IF(D21=0,0,'Financial Model'!D3/D21)</f>
         <v>0.2713095617414477</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="46">
         <f>IF(E21=0,0,'Financial Model'!E3/E21)</f>
         <v>0.20260480207657366</v>
       </c>
-      <c r="F31" s="44">
+      <c r="F31" s="46">
         <f>IF(F21=0,0,'Financial Model'!F3/F21)</f>
         <v>0.15898192310956463</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="B32" s="44">
+        <v>171</v>
+      </c>
+      <c r="B32" s="46">
         <f>IF(B21=0,0,'Financial Model'!B4/B21)</f>
         <v>0.41228668941979524</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="46">
         <f>IF(C21=0,0,'Financial Model'!C4/C21)</f>
         <v>0.3327293026451391</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="46">
         <f>IF(D21=0,0,'Financial Model'!D4/D21)</f>
         <v>0.2880601338238276</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="46">
         <f>IF(E21=0,0,'Financial Model'!E4/E21)</f>
         <v>0.26524334847501624</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="46">
         <f>IF(F21=0,0,'Financial Model'!F4/F21)</f>
         <v>0.24984248493592465</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="B33" s="48">
+        <v>172</v>
+      </c>
+      <c r="B33" s="50">
         <f>IF(B21=0,0,B25/B21)</f>
         <v>-0.01785938566552901</v>
       </c>
@@ -4801,7 +5117,7 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -4811,61 +5127,61 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="B36" s="44">
+        <v>174</v>
+      </c>
+      <c r="B36" s="46">
         <v>0.032764505119453925</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="46">
         <v>0.03538302988663689</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="46">
         <v>0.03684500188280277</v>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="46">
         <v>0.03781094527363184</v>
       </c>
-      <c r="F36" s="44">
+      <c r="F36" s="46">
         <v>0.03819061359585844</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="B37" s="44">
+        <v>175</v>
+      </c>
+      <c r="B37" s="46">
         <v>0.8477815699658703</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="46">
         <v>0.9066472002748196</v>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="46">
         <v>0.9356371114908901</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="46">
         <v>0.9502920181700195</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="46">
         <v>0.9507765424764492</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B38" s="44">
+        <v>176</v>
+      </c>
+      <c r="B38" s="46">
         <v>0.11945392491467577</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="46">
         <v>0.057969769838543454</v>
       </c>
-      <c r="D38" s="44">
+      <c r="D38" s="46">
         <v>0.0275178866263071</v>
       </c>
-      <c r="E38" s="44">
+      <c r="E38" s="46">
         <v>0.01189703655634869</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="46">
         <v>0.011032843927692439</v>
       </c>
     </row>
@@ -4913,26 +5229,26 @@
       <c r="H1" s="18"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="B2" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
+      <c r="B4" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
